--- a/data/uploads_local/사모_판매대본_한국투자반도체&코스닥일반사모투자신탁.xlsx
+++ b/data/uploads_local/사모_판매대본_한국투자반도체&코스닥일반사모투자신탁.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10426"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\펀드상품부\#상품설정\(074950~074951)한국투자반도체&amp;코스닥\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a114384/Desktop/2.KISAI/펀드 불완전판매/data/uploads_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A46DAA-059A-4DC6-8CA3-6B13F4ABA4CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089FA34F-0AD9-244D-9CAB-90FA45C42D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1" xr2:uid="{27046729-DC8E-4EC9-9EBE-9FEAE0333B25}"/>
+    <workbookView xWindow="17280" yWindow="760" windowWidth="17280" windowHeight="20440" activeTab="1" xr2:uid="{27046729-DC8E-4EC9-9EBE-9FEAE0333B25}"/>
   </bookViews>
   <sheets>
     <sheet name="(내점) 투자자정보(26.01.02)" sheetId="79" r:id="rId1"/>
@@ -23,13 +23,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'(내점) 투자자정보(26.01.02)'!$A$6:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사모펀드(내점)'!$A$6:$H$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'사모펀드(방문o,유선x)'!$A$6:$H$82</definedName>
+    <definedName name="부분합전체">#N/A</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'(내점) 투자자정보(26.01.02)'!$A$1:$G$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'사모펀드(내점)'!$A$1:$H$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'사모펀드(방문o,유선x)'!$A$1:$H$89</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'(내점) 투자자정보(26.01.02)'!$5:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'사모펀드(내점)'!$5:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'사모펀드(방문o,유선x)'!$5:$6</definedName>
-    <definedName name="부분합전체">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5661,9 +5661,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6435,7 +6435,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -6445,27 +6445,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="8" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6480,43 +6480,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6525,16 +6525,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6543,29 +6543,17 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -6576,28 +6564,19 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6609,9 +6588,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6642,9 +6618,6 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -6660,557 +6633,467 @@
     <xf numFmtId="0" fontId="38" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="19" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="19" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="19" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7933,406 +7816,405 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:G74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="3" customWidth="1"/>
     <col min="2" max="2" width="16" style="3" customWidth="1"/>
-    <col min="3" max="5" width="5.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44.625" style="1" customWidth="1"/>
+    <col min="3" max="5" width="5.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="92.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="151" t="s">
+    <row r="1" spans="1:7" ht="17">
+      <c r="A1" s="180" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="G2" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="8" t="s">
         <v>149</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>150</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="F4" s="88"/>
-    </row>
-    <row r="5" spans="1:7" s="89" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="153" t="s">
+    </row>
+    <row r="5" spans="1:7" s="66" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A5" s="149" t="s">
         <v>151</v>
       </c>
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="156" t="s">
+      <c r="C5" s="182" t="s">
         <v>152</v>
       </c>
-      <c r="D5" s="156" t="s">
+      <c r="D5" s="182" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="156"/>
-      <c r="F5" s="155" t="s">
+      <c r="E5" s="182"/>
+      <c r="F5" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="155" t="s">
+      <c r="G5" s="147" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="89" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="154"/>
-      <c r="B6" s="155"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="90" t="s">
+    <row r="6" spans="1:7" s="66" customFormat="1" ht="45">
+      <c r="A6" s="151"/>
+      <c r="B6" s="147"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="155"/>
-      <c r="G6" s="155"/>
-    </row>
-    <row r="7" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91" t="s">
+      <c r="F6" s="147"/>
+      <c r="G6" s="147"/>
+    </row>
+    <row r="7" spans="1:7" ht="58.5" customHeight="1">
+      <c r="A7" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="71" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="71" t="s">
+      <c r="E7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="92"/>
-      <c r="G7" s="93" t="s">
+      <c r="F7" s="69"/>
+      <c r="G7" s="70" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="157" t="s">
+    <row r="8" spans="1:7" ht="58.5" customHeight="1">
+      <c r="A8" s="183" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="159" t="s">
+      <c r="B8" s="185" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="161" t="s">
+      <c r="C8" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="161" t="s">
+      <c r="D8" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="161" t="s">
+      <c r="E8" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="149" t="s">
+      <c r="F8" s="178" t="s">
         <v>159</v>
       </c>
-      <c r="G8" s="94" t="s">
+      <c r="G8" s="71" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="158"/>
-      <c r="B9" s="160"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="162"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="95" t="s">
+    <row r="9" spans="1:7" ht="58.5" customHeight="1">
+      <c r="A9" s="184"/>
+      <c r="B9" s="186"/>
+      <c r="C9" s="188"/>
+      <c r="D9" s="188"/>
+      <c r="E9" s="188"/>
+      <c r="F9" s="179"/>
+      <c r="G9" s="72" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="145.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91" t="s">
+    <row r="10" spans="1:7" ht="145.5" customHeight="1">
+      <c r="A10" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="71" t="s">
+      <c r="C10" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="97" t="s">
+      <c r="G10" s="74" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="163" t="s">
+    <row r="11" spans="1:7" ht="50.25" customHeight="1">
+      <c r="A11" s="174" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="75" t="s">
         <v>166</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="166" t="s">
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="127" t="s">
         <v>167</v>
       </c>
-      <c r="G11" s="100" t="s">
+      <c r="G11" s="77" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="164"/>
-      <c r="B12" s="101" t="s">
+    <row r="12" spans="1:7" ht="50.25" customHeight="1">
+      <c r="A12" s="175"/>
+      <c r="B12" s="78" t="s">
         <v>169</v>
       </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="103" t="s">
+      <c r="C12" s="79"/>
+      <c r="D12" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="104" t="s">
+      <c r="E12" s="79"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="81" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="165"/>
-      <c r="B13" s="105" t="s">
+    <row r="13" spans="1:7" ht="50.25" customHeight="1">
+      <c r="A13" s="176"/>
+      <c r="B13" s="82" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="107" t="s">
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="168"/>
-      <c r="G13" s="108" t="s">
+      <c r="F13" s="129"/>
+      <c r="G13" s="85" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="72" t="s">
+    <row r="14" spans="1:7" ht="48">
+      <c r="A14" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="169" t="s">
+      <c r="B14" s="144" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="72" t="s">
+      <c r="E14" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="84" t="s">
+      <c r="F14" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="109" t="s">
+      <c r="G14" s="86" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="89.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="163" t="s">
+    <row r="15" spans="1:7" ht="89.25" customHeight="1">
+      <c r="A15" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="170"/>
-      <c r="C15" s="172" t="s">
+      <c r="B15" s="177"/>
+      <c r="C15" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="172" t="s">
+      <c r="D15" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="172" t="s">
+      <c r="E15" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="174" t="s">
+      <c r="F15" s="127" t="s">
         <v>176</v>
       </c>
-      <c r="G15" s="110" t="s">
+      <c r="G15" s="74" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="165"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="173"/>
-      <c r="F16" s="175"/>
-      <c r="G16" s="111" t="s">
+    <row r="16" spans="1:7" ht="13.5" customHeight="1">
+      <c r="A16" s="176"/>
+      <c r="B16" s="145"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="87" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="172" t="s">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
+      <c r="A17" s="122" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="176" t="s">
+      <c r="B17" s="112" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="172" t="s">
+      <c r="C17" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="178"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="174" t="s">
+      <c r="D17" s="172"/>
+      <c r="E17" s="172"/>
+      <c r="F17" s="127" t="s">
         <v>180</v>
       </c>
-      <c r="G17" s="174" t="s">
+      <c r="G17" s="127" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="173"/>
-      <c r="B18" s="177"/>
-      <c r="C18" s="173"/>
-      <c r="D18" s="179"/>
-      <c r="E18" s="179"/>
-      <c r="F18" s="175"/>
-      <c r="G18" s="175"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="90" customHeight="1">
+      <c r="A18" s="124"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="173"/>
+      <c r="E18" s="173"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+    </row>
+    <row r="35" spans="6:6">
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="6:6">
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="6:6">
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="6:6">
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="6:6">
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="6:6">
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="6:6">
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="6:6">
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="6:6">
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="6:6">
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="6:6">
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="6:6">
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="6:6">
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="6:6">
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="6:6">
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="6:6">
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="6:6">
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="6:6">
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="6:6">
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="6:6">
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="6:6">
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="6:6">
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="6:6">
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="6:6">
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="6:6">
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="6:6">
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="6:6">
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="6:6">
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="6:6">
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="6:6">
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="6:6">
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="6:6">
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="6:6">
       <c r="F67" s="2"/>
     </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="6:6">
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="6:6">
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="6:6">
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="6:6">
       <c r="F71" s="2"/>
     </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="6:6">
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="6:6">
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="6:6">
       <c r="F74" s="2"/>
     </row>
   </sheetData>
@@ -8340,21 +8222,6 @@
     <filterColumn colId="0" showButton="0"/>
   </autoFilter>
   <mergeCells count="28">
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:A6"/>
@@ -8368,6 +8235,21 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -8386,19 +8268,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H133"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="27.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="5.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46" style="1" customWidth="1"/>
-    <col min="8" max="8" width="111.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="111.1640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>221</v>
       </c>
@@ -8410,412 +8292,412 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="H2" s="9" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="155" t="s">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A5" s="147" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155" t="s">
+      <c r="B5" s="147"/>
+      <c r="C5" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="184" t="s">
+      <c r="D5" s="169" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="182" t="s">
+      <c r="E5" s="167" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="183"/>
-      <c r="G5" s="155" t="s">
+      <c r="F5" s="168"/>
+      <c r="G5" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="155" t="s">
+      <c r="H5" s="147" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="155"/>
-      <c r="B6" s="155"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="114" t="s">
+    <row r="6" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A6" s="147"/>
+      <c r="B6" s="147"/>
+      <c r="C6" s="147"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155"/>
-    </row>
-    <row r="7" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="180" t="s">
+      <c r="G6" s="147"/>
+      <c r="H6" s="147"/>
+    </row>
+    <row r="7" spans="1:8" ht="59.25" customHeight="1">
+      <c r="A7" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="180"/>
-      <c r="C7" s="192" t="s">
+      <c r="B7" s="134"/>
+      <c r="C7" s="136" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="187" t="s">
+      <c r="D7" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="187" t="s">
+      <c r="E7" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="215"/>
-      <c r="G7" s="181" t="s">
+      <c r="F7" s="132"/>
+      <c r="G7" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="H7" s="117" t="s">
+      <c r="H7" s="91" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="180"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="192"/>
-      <c r="D8" s="187"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="215"/>
-      <c r="G8" s="181"/>
+    <row r="8" spans="1:8" ht="58.5" customHeight="1">
+      <c r="A8" s="134"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="137"/>
       <c r="H8" s="13" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="168" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="180" t="s">
+    <row r="9" spans="1:8" ht="168" customHeight="1">
+      <c r="A9" s="134" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="180"/>
-      <c r="C9" s="81" t="s">
+      <c r="B9" s="134"/>
+      <c r="C9" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="E9" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="86"/>
-      <c r="G9" s="115" t="s">
+      <c r="F9" s="64"/>
+      <c r="G9" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H9" s="116" t="s">
+      <c r="H9" s="28" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="159.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="180"/>
-      <c r="B10" s="180"/>
-      <c r="C10" s="192" t="s">
+    <row r="10" spans="1:8" ht="159.75" customHeight="1">
+      <c r="A10" s="134"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="136" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="187" t="s">
+      <c r="D10" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="187" t="s">
+      <c r="E10" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="215"/>
-      <c r="G10" s="217" t="s">
+      <c r="F10" s="132"/>
+      <c r="G10" s="133" t="s">
         <v>189</v>
       </c>
-      <c r="H10" s="116" t="s">
+      <c r="H10" s="28" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="180"/>
-      <c r="B11" s="180"/>
-      <c r="C11" s="192"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="187"/>
-      <c r="F11" s="215"/>
-      <c r="G11" s="217"/>
-      <c r="H11" s="118" t="s">
+    <row r="11" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A11" s="134"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="92" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="180" t="s">
+    <row r="12" spans="1:8" ht="36.75" customHeight="1">
+      <c r="A12" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="180"/>
-      <c r="C12" s="186" t="s">
+      <c r="B12" s="134"/>
+      <c r="C12" s="130" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="187" t="s">
+      <c r="D12" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="187" t="s">
+      <c r="E12" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="215"/>
-      <c r="G12" s="181" t="s">
+      <c r="F12" s="132"/>
+      <c r="G12" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H12" s="181" t="s">
+      <c r="H12" s="137" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="180"/>
-      <c r="B13" s="180"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="187"/>
-      <c r="E13" s="187"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="181"/>
-    </row>
-    <row r="14" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="188" t="s">
+    <row r="13" spans="1:8" ht="36.75" customHeight="1">
+      <c r="A13" s="134"/>
+      <c r="B13" s="134"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+    </row>
+    <row r="14" spans="1:8" ht="108" customHeight="1">
+      <c r="A14" s="171" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="188"/>
-      <c r="C14" s="188"/>
-      <c r="D14" s="188"/>
-      <c r="E14" s="188"/>
-      <c r="F14" s="188"/>
-      <c r="G14" s="188"/>
-      <c r="H14" s="188"/>
-    </row>
-    <row r="15" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="180" t="s">
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="171"/>
+    </row>
+    <row r="15" spans="1:8" ht="58.5" customHeight="1">
+      <c r="A15" s="134" t="s">
         <v>196</v>
       </c>
-      <c r="B15" s="180"/>
-      <c r="C15" s="112" t="s">
+      <c r="B15" s="134"/>
+      <c r="C15" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="E15" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="86"/>
-      <c r="G15" s="113"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="89"/>
       <c r="H15" s="15" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="185" t="s">
+    <row r="16" spans="1:8" ht="96" customHeight="1">
+      <c r="A16" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="192" t="s">
+      <c r="B16" s="170"/>
+      <c r="C16" s="136" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="D16" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="187" t="s">
+      <c r="E16" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="215"/>
-      <c r="G16" s="218"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="135"/>
       <c r="H16" s="15" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="185"/>
-      <c r="B17" s="185"/>
-      <c r="C17" s="192"/>
-      <c r="D17" s="187"/>
-      <c r="E17" s="187"/>
-      <c r="F17" s="215"/>
-      <c r="G17" s="218"/>
-      <c r="H17" s="119" t="s">
+    <row r="17" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A17" s="170"/>
+      <c r="B17" s="170"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="93" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="185"/>
-      <c r="B18" s="185"/>
-      <c r="C18" s="192"/>
-      <c r="D18" s="187"/>
-      <c r="E18" s="187"/>
-      <c r="F18" s="215"/>
-      <c r="G18" s="218"/>
+    <row r="18" spans="1:8" ht="60" customHeight="1">
+      <c r="A18" s="170"/>
+      <c r="B18" s="170"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="135"/>
       <c r="H18" s="15" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="185"/>
-      <c r="B19" s="185"/>
-      <c r="C19" s="186" t="s">
+    <row r="19" spans="1:8" ht="105.75" customHeight="1">
+      <c r="A19" s="170"/>
+      <c r="B19" s="170"/>
+      <c r="C19" s="130" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="86"/>
-      <c r="G19" s="222" t="s">
+      <c r="F19" s="64"/>
+      <c r="G19" s="126" t="s">
         <v>204</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="185"/>
-      <c r="B20" s="185"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="72" t="s">
+    <row r="20" spans="1:8" ht="93.75" customHeight="1">
+      <c r="A20" s="170"/>
+      <c r="B20" s="170"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="72" t="s">
+      <c r="E20" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="86"/>
-      <c r="G20" s="222"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="126"/>
       <c r="H20" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="216" t="s">
+    <row r="21" spans="1:8" ht="39.75" customHeight="1">
+      <c r="A21" s="142" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="206"/>
-      <c r="C21" s="176" t="s">
+      <c r="B21" s="143"/>
+      <c r="C21" s="112" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="172" t="s">
+      <c r="D21" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="172" t="s">
+      <c r="E21" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="219"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="174" t="s">
+      <c r="F21" s="120"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="127" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="216"/>
-      <c r="B22" s="206"/>
-      <c r="C22" s="177"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="220"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="175"/>
-    </row>
-    <row r="23" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="228" t="s">
+    <row r="22" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A22" s="142"/>
+      <c r="B22" s="143"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="129"/>
+    </row>
+    <row r="23" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A23" s="118" t="s">
         <v>232</v>
       </c>
-      <c r="B23" s="229"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="136" t="s">
+      <c r="B23" s="119"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="104" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="227" t="s">
+    <row r="24" spans="1:8" ht="108" customHeight="1">
+      <c r="A24" s="117" t="s">
         <v>224</v>
       </c>
-      <c r="B24" s="227" t="s">
+      <c r="B24" s="117" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="176"/>
-      <c r="D24" s="172"/>
-      <c r="E24" s="172"/>
-      <c r="F24" s="219"/>
-      <c r="G24" s="174" t="s">
+      <c r="C24" s="112"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="127" t="s">
         <v>225</v>
       </c>
-      <c r="H24" s="131" t="s">
+      <c r="H24" s="99" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="225"/>
-      <c r="B25" s="225"/>
-      <c r="C25" s="224"/>
-      <c r="D25" s="195"/>
-      <c r="E25" s="195"/>
-      <c r="F25" s="221"/>
-      <c r="G25" s="223"/>
+    <row r="25" spans="1:8" ht="22.5" customHeight="1">
+      <c r="A25" s="115"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="128"/>
       <c r="H25" s="25" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A26" s="225"/>
-      <c r="B26" s="226"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="173"/>
-      <c r="E26" s="173"/>
-      <c r="F26" s="220"/>
-      <c r="G26" s="175"/>
+    <row r="26" spans="1:8" ht="32">
+      <c r="A26" s="115"/>
+      <c r="B26" s="116"/>
+      <c r="C26" s="114"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="129"/>
       <c r="H26" s="25" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="165" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="225"/>
-      <c r="B27" s="225" t="s">
+    <row r="27" spans="1:8" ht="165" customHeight="1">
+      <c r="A27" s="115"/>
+      <c r="B27" s="115" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="124"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="125"/>
-      <c r="G27" s="122" t="s">
+      <c r="C27" s="97"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="96" t="s">
         <v>226</v>
       </c>
-      <c r="H27" s="122" t="s">
+      <c r="H27" s="96" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="226"/>
-      <c r="B28" s="226"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="122"/>
-      <c r="H28" s="122" t="s">
+    <row r="28" spans="1:8" ht="23.25" customHeight="1">
+      <c r="A28" s="116"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="96" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="180" t="s">
+    <row r="29" spans="1:8" ht="58.5" customHeight="1">
+      <c r="A29" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="180"/>
+      <c r="B29" s="134"/>
       <c r="C29" s="33"/>
       <c r="D29" s="26" t="s">
         <v>0</v>
@@ -8826,399 +8708,399 @@
       <c r="F29" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="H29" s="47" t="s">
+      <c r="H29" s="213" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="191" t="s">
+    <row r="30" spans="1:8" ht="124.5" customHeight="1">
+      <c r="A30" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="191" t="s">
+      <c r="B30" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="192" t="s">
+      <c r="C30" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="172" t="s">
+      <c r="E30" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="172" t="s">
+      <c r="F30" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="G30" s="193" t="s">
+      <c r="G30" s="164" t="s">
         <v>142</v>
       </c>
-      <c r="H30" s="194" t="s">
+      <c r="H30" s="214" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="141" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="191"/>
-      <c r="B31" s="191"/>
-      <c r="C31" s="192"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="195"/>
-      <c r="F31" s="195"/>
-      <c r="G31" s="193"/>
-      <c r="H31" s="194"/>
-    </row>
-    <row r="32" spans="1:8" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="191"/>
-      <c r="B32" s="47" t="s">
+    <row r="31" spans="1:8" ht="175" customHeight="1">
+      <c r="A31" s="163"/>
+      <c r="B31" s="163"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="123"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="214"/>
+    </row>
+    <row r="32" spans="1:8" ht="285.75" customHeight="1">
+      <c r="A32" s="163"/>
+      <c r="B32" s="40" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="17"/>
-      <c r="D32" s="43" t="s">
+      <c r="D32" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="40" t="s">
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="164"/>
+      <c r="H32" s="36" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="191"/>
-      <c r="B33" s="62" t="s">
+    <row r="33" spans="1:8" ht="36.75" customHeight="1">
+      <c r="A33" s="163"/>
+      <c r="B33" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="196"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="26"/>
       <c r="E33"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="193"/>
-      <c r="H33" s="189" t="s">
+      <c r="F33" s="26"/>
+      <c r="G33" s="164"/>
+      <c r="H33" s="161" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="191"/>
-      <c r="B34" s="47" t="s">
+    <row r="34" spans="1:8" ht="78" customHeight="1">
+      <c r="A34" s="163"/>
+      <c r="B34" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="196"/>
-      <c r="D34" s="43" t="s">
+      <c r="C34" s="166"/>
+      <c r="D34" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E34" s="43" t="s">
+      <c r="E34" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G34" s="193"/>
-      <c r="H34" s="190"/>
-    </row>
-    <row r="35" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="191"/>
-      <c r="B35" s="62" t="s">
+      <c r="G34" s="164"/>
+      <c r="H34" s="162"/>
+    </row>
+    <row r="35" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A35" s="163"/>
+      <c r="B35" s="54" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="17"/>
-      <c r="D35" s="43" t="s">
+      <c r="D35" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="E35" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F35" s="43" t="s">
+      <c r="F35" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G35" s="193"/>
-      <c r="H35" s="55" t="s">
+      <c r="G35" s="164"/>
+      <c r="H35" s="47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="209">
+    <row r="36" spans="1:8" ht="153" customHeight="1">
+      <c r="A36" s="158">
         <v>2943</v>
       </c>
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="54" t="s">
         <v>54</v>
       </c>
       <c r="C36" s="17"/>
-      <c r="D36" s="43" t="s">
+      <c r="D36" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E36" s="43" t="s">
+      <c r="E36" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F36" s="43" t="s">
+      <c r="F36" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G36" s="49" t="s">
+      <c r="G36" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="H36" s="137" t="s">
+      <c r="H36" s="105" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="274.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="210"/>
-      <c r="B37" s="213" t="s">
+    <row r="37" spans="1:8" ht="274.5" customHeight="1">
+      <c r="A37" s="159"/>
+      <c r="B37" s="138" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="172" t="s">
+      <c r="C37" s="38"/>
+      <c r="D37" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="187" t="s">
+      <c r="E37" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="187" t="s">
+      <c r="F37" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="G37" s="48" t="s">
+      <c r="G37" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="138" t="s">
+      <c r="H37" s="106" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="298.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="210"/>
-      <c r="B38" s="214"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="195"/>
-      <c r="E38" s="187"/>
-      <c r="F38" s="187"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="139" t="s">
+    <row r="38" spans="1:8" ht="298.5" customHeight="1">
+      <c r="A38" s="159"/>
+      <c r="B38" s="139"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="123"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="131"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="107" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="189" x14ac:dyDescent="0.3">
-      <c r="A39" s="210"/>
-      <c r="B39" s="130"/>
-      <c r="C39" s="129"/>
-      <c r="D39" s="195"/>
-      <c r="E39" s="187"/>
-      <c r="F39" s="187"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="139" t="s">
+    <row r="39" spans="1:8" ht="224">
+      <c r="A39" s="159"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="123"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="131"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="107" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="273.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="210"/>
-      <c r="B40" s="130"/>
-      <c r="C40" s="129"/>
-      <c r="D40" s="195"/>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187"/>
-      <c r="G40" s="128"/>
-      <c r="H40" s="139" t="s">
+    <row r="40" spans="1:8" ht="273.75" customHeight="1">
+      <c r="A40" s="159"/>
+      <c r="B40" s="98"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="123"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="131"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="107" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="222" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="210"/>
-      <c r="B41" s="214" t="s">
+    <row r="41" spans="1:8" ht="222" customHeight="1">
+      <c r="A41" s="159"/>
+      <c r="B41" s="139" t="s">
         <v>144</v>
       </c>
-      <c r="C41" s="197"/>
-      <c r="D41" s="195"/>
-      <c r="E41" s="187"/>
-      <c r="F41" s="187"/>
-      <c r="G41" s="197"/>
-      <c r="H41" s="140" t="s">
+      <c r="C41" s="140"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="108" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="175.5" x14ac:dyDescent="0.3">
-      <c r="A42" s="210"/>
-      <c r="B42" s="214"/>
-      <c r="C42" s="198"/>
-      <c r="D42" s="195"/>
-      <c r="E42" s="187"/>
-      <c r="F42" s="187"/>
-      <c r="G42" s="199"/>
-      <c r="H42" s="140" t="s">
+    <row r="42" spans="1:8" ht="208">
+      <c r="A42" s="159"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="141"/>
+      <c r="D42" s="123"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="148"/>
+      <c r="H42" s="108" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="210"/>
-      <c r="B43" s="62" t="s">
+    <row r="43" spans="1:8" ht="16">
+      <c r="A43" s="159"/>
+      <c r="B43" s="54" t="s">
         <v>72</v>
       </c>
       <c r="C43" s="17"/>
-      <c r="D43" s="195"/>
-      <c r="E43" s="187"/>
-      <c r="F43" s="187"/>
-      <c r="G43" s="197"/>
+      <c r="D43" s="123"/>
+      <c r="E43" s="131"/>
+      <c r="F43" s="131"/>
+      <c r="G43" s="140"/>
       <c r="H43" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="210"/>
-      <c r="B44" s="62" t="s">
+    <row r="44" spans="1:8" ht="16">
+      <c r="A44" s="159"/>
+      <c r="B44" s="54" t="s">
         <v>73</v>
       </c>
       <c r="C44" s="17"/>
-      <c r="D44" s="195"/>
-      <c r="E44" s="187"/>
-      <c r="F44" s="187"/>
-      <c r="G44" s="198"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="131"/>
+      <c r="F44" s="131"/>
+      <c r="G44" s="141"/>
       <c r="H44" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="210"/>
-      <c r="B45" s="62" t="s">
+    <row r="45" spans="1:8" ht="16">
+      <c r="A45" s="159"/>
+      <c r="B45" s="54" t="s">
         <v>74</v>
       </c>
       <c r="C45" s="17"/>
-      <c r="D45" s="195"/>
-      <c r="E45" s="187"/>
-      <c r="F45" s="187"/>
-      <c r="G45" s="198"/>
+      <c r="D45" s="123"/>
+      <c r="E45" s="131"/>
+      <c r="F45" s="131"/>
+      <c r="G45" s="141"/>
       <c r="H45" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="210"/>
-      <c r="B46" s="62" t="s">
+    <row r="46" spans="1:8" ht="16">
+      <c r="A46" s="159"/>
+      <c r="B46" s="54" t="s">
         <v>75</v>
       </c>
       <c r="C46" s="17"/>
-      <c r="D46" s="195"/>
-      <c r="E46" s="187"/>
-      <c r="F46" s="187"/>
-      <c r="G46" s="198"/>
+      <c r="D46" s="123"/>
+      <c r="E46" s="131"/>
+      <c r="F46" s="131"/>
+      <c r="G46" s="141"/>
       <c r="H46" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="210"/>
-      <c r="B47" s="62" t="s">
+    <row r="47" spans="1:8" ht="16">
+      <c r="A47" s="159"/>
+      <c r="B47" s="54" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="17"/>
-      <c r="D47" s="195"/>
-      <c r="E47" s="187"/>
-      <c r="F47" s="187"/>
-      <c r="G47" s="198"/>
+      <c r="D47" s="123"/>
+      <c r="E47" s="131"/>
+      <c r="F47" s="131"/>
+      <c r="G47" s="141"/>
       <c r="H47" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="210"/>
-      <c r="B48" s="62" t="s">
+    <row r="48" spans="1:8" ht="16">
+      <c r="A48" s="159"/>
+      <c r="B48" s="54" t="s">
         <v>77</v>
       </c>
       <c r="C48" s="17"/>
-      <c r="D48" s="195"/>
-      <c r="E48" s="187"/>
-      <c r="F48" s="187"/>
-      <c r="G48" s="198"/>
+      <c r="D48" s="123"/>
+      <c r="E48" s="131"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="141"/>
       <c r="H48" s="12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="210"/>
-      <c r="B49" s="62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="16">
+      <c r="A49" s="159"/>
+      <c r="B49" s="54" t="s">
         <v>78</v>
       </c>
       <c r="C49" s="17"/>
-      <c r="D49" s="195"/>
-      <c r="E49" s="187"/>
-      <c r="F49" s="187"/>
-      <c r="G49" s="198"/>
+      <c r="D49" s="123"/>
+      <c r="E49" s="131"/>
+      <c r="F49" s="131"/>
+      <c r="G49" s="141"/>
       <c r="H49" s="12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="210"/>
-      <c r="B50" s="62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="16">
+      <c r="A50" s="159"/>
+      <c r="B50" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="17"/>
-      <c r="D50" s="195"/>
-      <c r="E50" s="187"/>
-      <c r="F50" s="187"/>
-      <c r="G50" s="198"/>
+      <c r="D50" s="123"/>
+      <c r="E50" s="131"/>
+      <c r="F50" s="131"/>
+      <c r="G50" s="141"/>
       <c r="H50" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="210"/>
-      <c r="B51" s="62" t="s">
+    <row r="51" spans="1:8" ht="16">
+      <c r="A51" s="159"/>
+      <c r="B51" s="54" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="17"/>
-      <c r="D51" s="195"/>
-      <c r="E51" s="187"/>
-      <c r="F51" s="187"/>
-      <c r="G51" s="198"/>
+      <c r="D51" s="123"/>
+      <c r="E51" s="131"/>
+      <c r="F51" s="131"/>
+      <c r="G51" s="141"/>
       <c r="H51" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="210"/>
-      <c r="B52" s="62" t="s">
+    <row r="52" spans="1:8" ht="18" customHeight="1">
+      <c r="A52" s="159"/>
+      <c r="B52" s="54" t="s">
         <v>88</v>
       </c>
       <c r="C52" s="17"/>
-      <c r="D52" s="195"/>
-      <c r="E52" s="187"/>
-      <c r="F52" s="187"/>
-      <c r="G52" s="198"/>
+      <c r="D52" s="123"/>
+      <c r="E52" s="131"/>
+      <c r="F52" s="131"/>
+      <c r="G52" s="141"/>
       <c r="H52" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A53" s="210"/>
-      <c r="B53" s="62" t="s">
+    <row r="53" spans="1:8" ht="32">
+      <c r="A53" s="159"/>
+      <c r="B53" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C53" s="17"/>
-      <c r="D53" s="195"/>
-      <c r="E53" s="187"/>
-      <c r="F53" s="187"/>
-      <c r="G53" s="198"/>
-      <c r="H53" s="57" t="s">
+      <c r="D53" s="123"/>
+      <c r="E53" s="131"/>
+      <c r="F53" s="131"/>
+      <c r="G53" s="141"/>
+      <c r="H53" s="49" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="210"/>
-      <c r="B54" s="62" t="s">
+    <row r="54" spans="1:8" ht="39.75" customHeight="1">
+      <c r="A54" s="159"/>
+      <c r="B54" s="54" t="s">
         <v>127</v>
       </c>
       <c r="C54" s="17"/>
-      <c r="D54" s="195"/>
-      <c r="E54" s="187"/>
-      <c r="F54" s="187"/>
-      <c r="G54" s="199"/>
-      <c r="H54" s="57" t="s">
+      <c r="D54" s="123"/>
+      <c r="E54" s="131"/>
+      <c r="F54" s="131"/>
+      <c r="G54" s="148"/>
+      <c r="H54" s="49" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="24.75" x14ac:dyDescent="0.3">
-      <c r="A55" s="210"/>
-      <c r="B55" s="52" t="s">
+    <row r="55" spans="1:8" ht="48">
+      <c r="A55" s="159"/>
+      <c r="B55" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C55" s="45" t="s">
+      <c r="C55" s="39" t="s">
         <v>129</v>
       </c>
       <c r="D55" s="26" t="s">
@@ -9231,55 +9113,55 @@
         <v>70</v>
       </c>
       <c r="G55" s="31"/>
-      <c r="H55" s="41" t="s">
+      <c r="H55" s="37" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="210"/>
-      <c r="B56" s="62" t="s">
+    <row r="56" spans="1:8" ht="44.25" customHeight="1">
+      <c r="A56" s="159"/>
+      <c r="B56" s="54" t="s">
         <v>79</v>
       </c>
       <c r="C56" s="17"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="57" t="s">
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="49" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="210"/>
-      <c r="B57" s="62" t="s">
+    <row r="57" spans="1:8" ht="44.25" customHeight="1">
+      <c r="A57" s="159"/>
+      <c r="B57" s="54" t="s">
         <v>89</v>
       </c>
       <c r="C57" s="17"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="57" t="s">
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="49" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A58" s="210"/>
-      <c r="B58" s="62" t="s">
+    <row r="58" spans="1:8" ht="32">
+      <c r="A58" s="159"/>
+      <c r="B58" s="54" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="17"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="56" t="s">
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="48" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="24.75" x14ac:dyDescent="0.3">
-      <c r="A59" s="210"/>
-      <c r="B59" s="62" t="s">
+    <row r="59" spans="1:8" ht="30">
+      <c r="A59" s="159"/>
+      <c r="B59" s="54" t="s">
         <v>80</v>
       </c>
       <c r="C59" s="31"/>
@@ -9293,131 +9175,131 @@
         <v>70</v>
       </c>
       <c r="G59" s="31"/>
-      <c r="H59" s="56" t="s">
+      <c r="H59" s="48" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="39" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="211"/>
-      <c r="B60" s="62" t="s">
+    <row r="60" spans="1:8" s="35" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A60" s="160"/>
+      <c r="B60" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="45" t="s">
+      <c r="C60" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="D60" s="43" t="s">
+      <c r="D60" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E60" s="43" t="s">
+      <c r="E60" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F60" s="43" t="s">
+      <c r="F60" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G60" s="38"/>
-      <c r="H60" s="58" t="s">
+      <c r="G60" s="28"/>
+      <c r="H60" s="50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="203" t="s">
+    <row r="61" spans="1:8" ht="27" customHeight="1">
+      <c r="A61" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="204"/>
-      <c r="C61" s="192"/>
-      <c r="D61" s="187" t="s">
+      <c r="B61" s="154"/>
+      <c r="C61" s="136"/>
+      <c r="D61" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E61" s="187" t="s">
+      <c r="E61" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="187" t="s">
+      <c r="F61" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="G61" s="200" t="s">
+      <c r="G61" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="50" t="s">
+      <c r="H61" s="43" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="205"/>
-      <c r="B62" s="206"/>
-      <c r="C62" s="192"/>
-      <c r="D62" s="187"/>
-      <c r="E62" s="187"/>
-      <c r="F62" s="187"/>
-      <c r="G62" s="200"/>
+    <row r="62" spans="1:8" ht="27" customHeight="1">
+      <c r="A62" s="155"/>
+      <c r="B62" s="143"/>
+      <c r="C62" s="136"/>
+      <c r="D62" s="131"/>
+      <c r="E62" s="131"/>
+      <c r="F62" s="131"/>
+      <c r="G62" s="133"/>
       <c r="H62" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="205"/>
-      <c r="B63" s="206"/>
-      <c r="C63" s="192"/>
-      <c r="D63" s="187"/>
-      <c r="E63" s="187"/>
-      <c r="F63" s="187"/>
-      <c r="G63" s="200"/>
-      <c r="H63" s="50" t="s">
+    <row r="63" spans="1:8" ht="27" customHeight="1">
+      <c r="A63" s="155"/>
+      <c r="B63" s="143"/>
+      <c r="C63" s="136"/>
+      <c r="D63" s="131"/>
+      <c r="E63" s="131"/>
+      <c r="F63" s="131"/>
+      <c r="G63" s="133"/>
+      <c r="H63" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="205"/>
-      <c r="B64" s="206"/>
-      <c r="C64" s="192"/>
-      <c r="D64" s="187"/>
-      <c r="E64" s="187"/>
-      <c r="F64" s="187"/>
-      <c r="G64" s="200"/>
+    <row r="64" spans="1:8" ht="27" customHeight="1">
+      <c r="A64" s="155"/>
+      <c r="B64" s="143"/>
+      <c r="C64" s="136"/>
+      <c r="D64" s="131"/>
+      <c r="E64" s="131"/>
+      <c r="F64" s="131"/>
+      <c r="G64" s="133"/>
       <c r="H64" s="18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="205"/>
-      <c r="B65" s="206"/>
-      <c r="C65" s="192"/>
-      <c r="D65" s="187"/>
-      <c r="E65" s="187"/>
-      <c r="F65" s="187"/>
-      <c r="G65" s="200"/>
-      <c r="H65" s="50" t="s">
+    <row r="65" spans="1:8" ht="27" customHeight="1">
+      <c r="A65" s="155"/>
+      <c r="B65" s="143"/>
+      <c r="C65" s="136"/>
+      <c r="D65" s="131"/>
+      <c r="E65" s="131"/>
+      <c r="F65" s="131"/>
+      <c r="G65" s="133"/>
+      <c r="H65" s="43" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="205"/>
-      <c r="B66" s="206"/>
-      <c r="C66" s="192"/>
-      <c r="D66" s="187"/>
-      <c r="E66" s="187"/>
-      <c r="F66" s="187"/>
-      <c r="G66" s="200"/>
+    <row r="66" spans="1:8" ht="27" customHeight="1">
+      <c r="A66" s="155"/>
+      <c r="B66" s="143"/>
+      <c r="C66" s="136"/>
+      <c r="D66" s="131"/>
+      <c r="E66" s="131"/>
+      <c r="F66" s="131"/>
+      <c r="G66" s="133"/>
       <c r="H66" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="207"/>
-      <c r="B67" s="208"/>
-      <c r="C67" s="192"/>
-      <c r="D67" s="187"/>
-      <c r="E67" s="187"/>
-      <c r="F67" s="187"/>
-      <c r="G67" s="200"/>
-      <c r="H67" s="50" t="s">
+    <row r="67" spans="1:8" ht="27" customHeight="1">
+      <c r="A67" s="156"/>
+      <c r="B67" s="157"/>
+      <c r="C67" s="136"/>
+      <c r="D67" s="131"/>
+      <c r="E67" s="131"/>
+      <c r="F67" s="131"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="54" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="180" t="s">
+    <row r="68" spans="1:8" ht="64" hidden="1">
+      <c r="A68" s="134" t="s">
         <v>64</v>
       </c>
-      <c r="B68" s="61"/>
+      <c r="B68" s="53"/>
       <c r="C68" s="29" t="s">
         <v>62</v>
       </c>
@@ -9433,13 +9315,13 @@
       <c r="G68" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H68" s="51" t="s">
+      <c r="H68" s="44" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A69" s="180"/>
-      <c r="B69" s="61" t="s">
+    <row r="69" spans="1:8" ht="64">
+      <c r="A69" s="134"/>
+      <c r="B69" s="53" t="s">
         <v>65</v>
       </c>
       <c r="C69" s="27"/>
@@ -9455,18 +9337,18 @@
       <c r="G69" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H69" s="51" t="s">
+      <c r="H69" s="44" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A70" s="61" t="s">
+    <row r="70" spans="1:8" ht="64">
+      <c r="A70" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B70" s="61" t="s">
+      <c r="B70" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C70" s="63" t="s">
+      <c r="C70" s="55" t="s">
         <v>46</v>
       </c>
       <c r="D70" s="26" t="s">
@@ -9481,61 +9363,61 @@
       <c r="G70" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="H70" s="51" t="s">
+      <c r="H70" s="44" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71" s="11" t="s">
         <v>50</v>
       </c>
       <c r="B71" s="10"/>
       <c r="C71" s="1"/>
     </row>
-    <row r="72" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="153" t="s">
+    <row r="72" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A72" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="B72" s="201"/>
-      <c r="C72" s="155" t="s">
+      <c r="B72" s="150"/>
+      <c r="C72" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="D72" s="77" t="s">
+      <c r="D72" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="77"/>
-      <c r="F72" s="212" t="s">
+      <c r="E72" s="62"/>
+      <c r="F72" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="155" t="s">
+      <c r="G72" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="H72" s="155" t="s">
+      <c r="H72" s="147" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="154"/>
-      <c r="B73" s="202"/>
-      <c r="C73" s="155"/>
+    <row r="73" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A73" s="151"/>
+      <c r="B73" s="152"/>
+      <c r="C73" s="147"/>
       <c r="D73" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F73" s="212"/>
-      <c r="G73" s="155"/>
-      <c r="H73" s="155"/>
-    </row>
-    <row r="74" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="172" t="s">
+      <c r="F73" s="146"/>
+      <c r="G73" s="147"/>
+      <c r="H73" s="147"/>
+    </row>
+    <row r="74" spans="1:8" ht="91.5" customHeight="1">
+      <c r="A74" s="122" t="s">
         <v>61</v>
       </c>
       <c r="B74" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C74" s="169" t="s">
+      <c r="C74" s="144" t="s">
         <v>82</v>
       </c>
       <c r="D74" s="22" t="s">
@@ -9547,19 +9429,19 @@
       <c r="F74" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G74" s="174" t="s">
+      <c r="G74" s="127" t="s">
         <v>83</v>
       </c>
       <c r="H74" s="21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="195"/>
+    <row r="75" spans="1:8" ht="124.5" customHeight="1">
+      <c r="A75" s="123"/>
       <c r="B75" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="171"/>
+      <c r="C75" s="145"/>
       <c r="D75" s="34" t="s">
         <v>5</v>
       </c>
@@ -9569,286 +9451,286 @@
       <c r="F75" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G75" s="175"/>
+      <c r="G75" s="129"/>
       <c r="H75" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="173"/>
+    <row r="76" spans="1:8" ht="77.25" customHeight="1">
+      <c r="A76" s="124"/>
       <c r="B76" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C76" s="37" t="s">
+      <c r="C76" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="D76" s="35" t="s">
+      <c r="D76" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E76" s="35" t="s">
+      <c r="E76" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="F76" s="35" t="s">
+      <c r="F76" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="G76" s="38" t="s">
+      <c r="G76" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H76" s="38" t="s">
+      <c r="H76" s="28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="191.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="43" t="s">
+    <row r="77" spans="1:8" ht="191.25" customHeight="1">
+      <c r="A77" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B77" s="43"/>
-      <c r="C77" s="36"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="60" t="s">
+      <c r="B77" s="26"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="H77" s="44" t="s">
+      <c r="H77" s="28" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="G94" s="2"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="G95" s="2"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="G96" s="2"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="G97" s="2"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="G98" s="2"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="G99" s="2"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="G100" s="2"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="G102" s="2"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="G113" s="2"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="G115" s="2"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="G116" s="2"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="G118" s="2"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="G119" s="2"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="G120" s="2"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="G121" s="2"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="G122" s="2"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="G124" s="2"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="G125" s="2"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="G126" s="2"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="G127" s="2"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="G128" s="2"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="G129" s="2"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="G130" s="2"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="G131" s="2"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -9856,28 +9738,53 @@
     </row>
   </sheetData>
   <mergeCells count="85">
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="A9:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A16:B20"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="G30:G35"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G43:G54"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="E61:E67"/>
+    <mergeCell ref="F61:F67"/>
+    <mergeCell ref="G61:G67"/>
+    <mergeCell ref="F37:F54"/>
+    <mergeCell ref="A72:B73"/>
+    <mergeCell ref="A61:B67"/>
+    <mergeCell ref="C61:C67"/>
+    <mergeCell ref="D61:D67"/>
+    <mergeCell ref="A36:A60"/>
+    <mergeCell ref="D37:D54"/>
+    <mergeCell ref="E37:E54"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="B41:B42"/>
@@ -9894,53 +9801,28 @@
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="F16:F18"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="G43:G54"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="E61:E67"/>
-    <mergeCell ref="F61:F67"/>
-    <mergeCell ref="G61:G67"/>
-    <mergeCell ref="F37:F54"/>
-    <mergeCell ref="A72:B73"/>
-    <mergeCell ref="A61:B67"/>
-    <mergeCell ref="C61:C67"/>
-    <mergeCell ref="D61:D67"/>
-    <mergeCell ref="A36:A60"/>
-    <mergeCell ref="D37:D54"/>
-    <mergeCell ref="E37:E54"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="G30:G35"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A16:B20"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="A9:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B24:B26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9964,19 +9846,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="27.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="5.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="47.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="114.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="47.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="114.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>221</v>
       </c>
@@ -9988,1324 +9870,1324 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="H2" s="9" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="155" t="s">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A5" s="147" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155" t="s">
+      <c r="B5" s="147"/>
+      <c r="C5" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="184" t="s">
+      <c r="D5" s="169" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="182" t="s">
+      <c r="E5" s="167" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="183"/>
-      <c r="G5" s="155" t="s">
+      <c r="F5" s="168"/>
+      <c r="G5" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="155" t="s">
+      <c r="H5" s="147" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="155"/>
-      <c r="B6" s="155"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="114" t="s">
+    <row r="6" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A6" s="147"/>
+      <c r="B6" s="147"/>
+      <c r="C6" s="147"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155"/>
-    </row>
-    <row r="7" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="153" t="s">
+      <c r="G6" s="147"/>
+      <c r="H6" s="147"/>
+    </row>
+    <row r="7" spans="1:8" ht="176">
+      <c r="A7" s="149" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="201"/>
-      <c r="C7" s="197" t="s">
+      <c r="B7" s="150"/>
+      <c r="C7" s="140" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="172" t="s">
+      <c r="D7" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="172" t="s">
+      <c r="E7" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="230"/>
-      <c r="G7" s="237" t="s">
+      <c r="F7" s="191"/>
+      <c r="G7" s="200" t="s">
         <v>214</v>
       </c>
-      <c r="H7" s="87" t="s">
+      <c r="H7" s="65" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="235"/>
-      <c r="B8" s="236"/>
-      <c r="C8" s="198"/>
-      <c r="D8" s="195"/>
-      <c r="E8" s="195"/>
-      <c r="F8" s="231"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="59" t="s">
+    <row r="8" spans="1:8" ht="80">
+      <c r="A8" s="198"/>
+      <c r="B8" s="199"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="201"/>
+      <c r="H8" s="51" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="235"/>
-      <c r="B9" s="236"/>
-      <c r="C9" s="198"/>
-      <c r="D9" s="195"/>
-      <c r="E9" s="195"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="238"/>
+    <row r="9" spans="1:8" ht="48">
+      <c r="A9" s="198"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="141"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="195"/>
+      <c r="G9" s="201"/>
       <c r="H9" s="13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="108" x14ac:dyDescent="0.3">
-      <c r="A10" s="235"/>
-      <c r="B10" s="236"/>
-      <c r="C10" s="198"/>
-      <c r="D10" s="195"/>
-      <c r="E10" s="195"/>
-      <c r="F10" s="231"/>
-      <c r="G10" s="238"/>
+    <row r="10" spans="1:8" ht="128">
+      <c r="A10" s="198"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="195"/>
+      <c r="G10" s="201"/>
       <c r="H10" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="154"/>
-      <c r="B11" s="202"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="173"/>
-      <c r="F11" s="232"/>
-      <c r="G11" s="239"/>
+    <row r="11" spans="1:8" ht="48">
+      <c r="A11" s="151"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="192"/>
+      <c r="G11" s="202"/>
       <c r="H11" s="30" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="173.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="233" t="s">
+    <row r="12" spans="1:8" ht="173.25" customHeight="1">
+      <c r="A12" s="196" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="234"/>
-      <c r="C12" s="78" t="s">
+      <c r="B12" s="197"/>
+      <c r="C12" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="120" t="s">
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="94" t="s">
         <v>215</v>
       </c>
       <c r="H12" s="30" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="173.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="233" t="s">
+    <row r="13" spans="1:8" ht="173.25" customHeight="1">
+      <c r="A13" s="196" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="234"/>
-      <c r="C13" s="78" t="s">
+      <c r="B13" s="197"/>
+      <c r="C13" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="120" t="s">
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="94" t="s">
         <v>68</v>
       </c>
       <c r="H13" s="30" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="216" x14ac:dyDescent="0.3">
-      <c r="A14" s="233" t="s">
+    <row r="14" spans="1:8" ht="256">
+      <c r="A14" s="196" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="234"/>
-      <c r="C14" s="78" t="s">
+      <c r="B14" s="197"/>
+      <c r="C14" s="63" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="120" t="s">
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="94" t="s">
         <v>41</v>
       </c>
       <c r="H14" s="30" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="322.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="233" t="s">
+    <row r="15" spans="1:8" ht="322.5" customHeight="1">
+      <c r="A15" s="196" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="234"/>
-      <c r="C15" s="144" t="s">
+      <c r="B15" s="197"/>
+      <c r="C15" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="147" t="s">
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="94" t="s">
         <v>238</v>
       </c>
       <c r="H15" s="30" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="153" t="s">
+    <row r="16" spans="1:8" ht="76.5" customHeight="1">
+      <c r="A16" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="201"/>
-      <c r="C16" s="197" t="s">
+      <c r="B16" s="150"/>
+      <c r="C16" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="172"/>
-      <c r="E16" s="172"/>
-      <c r="F16" s="230"/>
-      <c r="G16" s="87" t="s">
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="191"/>
+      <c r="G16" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="84" t="s">
+      <c r="H16" s="28" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="154"/>
-      <c r="B17" s="202"/>
-      <c r="C17" s="199"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="232"/>
-      <c r="G17" s="87" t="s">
+    <row r="17" spans="1:8" ht="58.5" customHeight="1">
+      <c r="A17" s="151"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="192"/>
+      <c r="G17" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="84" t="s">
+      <c r="H17" s="28" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="153" t="s">
+    <row r="18" spans="1:8" ht="35.25" customHeight="1">
+      <c r="A18" s="149" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="201"/>
-      <c r="C18" s="197" t="s">
+      <c r="B18" s="150"/>
+      <c r="C18" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="172"/>
-      <c r="E18" s="172"/>
-      <c r="F18" s="230"/>
-      <c r="G18" s="242" t="s">
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="191"/>
+      <c r="G18" s="193" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="54" t="s">
+      <c r="H18" s="46" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="154"/>
-      <c r="B19" s="202"/>
-      <c r="C19" s="199"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="232"/>
-      <c r="G19" s="243"/>
+    <row r="19" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A19" s="151"/>
+      <c r="B19" s="152"/>
+      <c r="C19" s="148"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="192"/>
+      <c r="G19" s="194"/>
       <c r="H19" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="168" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="180" t="s">
+    <row r="20" spans="1:8" ht="168" customHeight="1">
+      <c r="A20" s="134" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="180"/>
-      <c r="C20" s="81" t="s">
+      <c r="B20" s="134"/>
+      <c r="C20" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="D20" s="72" t="s">
+      <c r="D20" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="72" t="s">
+      <c r="E20" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="86"/>
-      <c r="G20" s="115" t="s">
+      <c r="F20" s="64"/>
+      <c r="G20" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="116" t="s">
+      <c r="H20" s="28" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="180"/>
-      <c r="B21" s="180"/>
-      <c r="C21" s="192" t="s">
+    <row r="21" spans="1:8" ht="153.75" customHeight="1">
+      <c r="A21" s="134"/>
+      <c r="B21" s="134"/>
+      <c r="C21" s="136" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="187" t="s">
+      <c r="D21" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="187" t="s">
+      <c r="E21" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="215"/>
-      <c r="G21" s="217" t="s">
+      <c r="F21" s="132"/>
+      <c r="G21" s="133" t="s">
         <v>189</v>
       </c>
-      <c r="H21" s="116" t="s">
+      <c r="H21" s="28" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="180"/>
-      <c r="B22" s="180"/>
-      <c r="C22" s="192"/>
-      <c r="D22" s="187"/>
-      <c r="E22" s="187"/>
-      <c r="F22" s="215"/>
-      <c r="G22" s="217"/>
-      <c r="H22" s="118" t="s">
+    <row r="22" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A22" s="134"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="92" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="180" t="s">
+    <row r="23" spans="1:8" ht="36.75" customHeight="1">
+      <c r="A23" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="B23" s="180"/>
-      <c r="C23" s="186" t="s">
+      <c r="B23" s="134"/>
+      <c r="C23" s="130" t="s">
         <v>192</v>
       </c>
-      <c r="D23" s="187" t="s">
+      <c r="D23" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="187" t="s">
+      <c r="E23" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="215"/>
-      <c r="G23" s="181" t="s">
+      <c r="F23" s="132"/>
+      <c r="G23" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H23" s="181" t="s">
+      <c r="H23" s="137" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="180"/>
-      <c r="B24" s="180"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="187"/>
-      <c r="E24" s="187"/>
-      <c r="F24" s="215"/>
-      <c r="G24" s="181"/>
-      <c r="H24" s="181"/>
-    </row>
-    <row r="25" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="188" t="s">
+    <row r="24" spans="1:8" ht="36.75" customHeight="1">
+      <c r="A24" s="134"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="137"/>
+    </row>
+    <row r="25" spans="1:8" ht="108" customHeight="1">
+      <c r="A25" s="171" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="188"/>
-      <c r="C25" s="188"/>
-      <c r="D25" s="188"/>
-      <c r="E25" s="188"/>
-      <c r="F25" s="188"/>
-      <c r="G25" s="188"/>
-      <c r="H25" s="188"/>
-    </row>
-    <row r="26" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="180" t="s">
+      <c r="B25" s="171"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="171"/>
+      <c r="H25" s="171"/>
+    </row>
+    <row r="26" spans="1:8" ht="58.5" customHeight="1">
+      <c r="A26" s="134" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="180"/>
-      <c r="C26" s="112" t="s">
+      <c r="B26" s="134"/>
+      <c r="C26" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D26" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="72" t="s">
+      <c r="E26" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="86"/>
-      <c r="G26" s="113"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="89"/>
       <c r="H26" s="15" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="185" t="s">
+    <row r="27" spans="1:8" ht="96" customHeight="1">
+      <c r="A27" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="185"/>
-      <c r="C27" s="192" t="s">
+      <c r="B27" s="170"/>
+      <c r="C27" s="136" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="187" t="s">
+      <c r="D27" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="187" t="s">
+      <c r="E27" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="215"/>
-      <c r="G27" s="218"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="135"/>
       <c r="H27" s="15" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="185"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="192"/>
-      <c r="D28" s="187"/>
-      <c r="E28" s="187"/>
-      <c r="F28" s="215"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="119" t="s">
+    <row r="28" spans="1:8" ht="33.75" customHeight="1">
+      <c r="A28" s="170"/>
+      <c r="B28" s="170"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="93" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="185"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="192"/>
-      <c r="D29" s="187"/>
-      <c r="E29" s="187"/>
-      <c r="F29" s="215"/>
-      <c r="G29" s="218"/>
+    <row r="29" spans="1:8" ht="60" customHeight="1">
+      <c r="A29" s="170"/>
+      <c r="B29" s="170"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="135"/>
       <c r="H29" s="15" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="185"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="186" t="s">
+    <row r="30" spans="1:8" ht="105.75" customHeight="1">
+      <c r="A30" s="170"/>
+      <c r="B30" s="170"/>
+      <c r="C30" s="130" t="s">
         <v>203</v>
       </c>
-      <c r="D30" s="72" t="s">
+      <c r="D30" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="72" t="s">
+      <c r="E30" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="86"/>
-      <c r="G30" s="222" t="s">
+      <c r="F30" s="64"/>
+      <c r="G30" s="126" t="s">
         <v>204</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="185"/>
-      <c r="B31" s="185"/>
-      <c r="C31" s="186"/>
-      <c r="D31" s="72" t="s">
+    <row r="31" spans="1:8" ht="93.75" customHeight="1">
+      <c r="A31" s="170"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="130"/>
+      <c r="D31" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E31" s="72" t="s">
+      <c r="E31" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F31" s="86"/>
-      <c r="G31" s="222"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="126"/>
       <c r="H31" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="216" t="s">
+    <row r="32" spans="1:8" ht="39.75" customHeight="1">
+      <c r="A32" s="142" t="s">
         <v>207</v>
       </c>
-      <c r="B32" s="206"/>
-      <c r="C32" s="176" t="s">
+      <c r="B32" s="143"/>
+      <c r="C32" s="112" t="s">
         <v>208</v>
       </c>
-      <c r="D32" s="172" t="s">
+      <c r="D32" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="172" t="s">
+      <c r="E32" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="219"/>
-      <c r="G32" s="174"/>
-      <c r="H32" s="174" t="s">
+      <c r="F32" s="120"/>
+      <c r="G32" s="127"/>
+      <c r="H32" s="127" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="216"/>
-      <c r="B33" s="206"/>
-      <c r="C33" s="177"/>
-      <c r="D33" s="173"/>
-      <c r="E33" s="173"/>
-      <c r="F33" s="220"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="175"/>
-    </row>
-    <row r="34" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="228" t="s">
+    <row r="33" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A33" s="142"/>
+      <c r="B33" s="143"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="129"/>
+      <c r="H33" s="129"/>
+    </row>
+    <row r="34" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A34" s="118" t="s">
         <v>233</v>
       </c>
-      <c r="B34" s="229"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="134"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="136" t="s">
+      <c r="B34" s="119"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="104" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="227" t="s">
+    <row r="35" spans="1:8" ht="48">
+      <c r="A35" s="117" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="227" t="s">
+      <c r="B35" s="117" t="s">
         <v>222</v>
       </c>
-      <c r="C35" s="176"/>
-      <c r="D35" s="172"/>
-      <c r="E35" s="172"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="174" t="s">
+      <c r="C35" s="112"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="127" t="s">
         <v>225</v>
       </c>
-      <c r="H35" s="131" t="s">
+      <c r="H35" s="99" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="225"/>
-      <c r="B36" s="225"/>
-      <c r="C36" s="224"/>
-      <c r="D36" s="195"/>
-      <c r="E36" s="195"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="223"/>
+    <row r="36" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A36" s="115"/>
+      <c r="B36" s="115"/>
+      <c r="C36" s="113"/>
+      <c r="D36" s="123"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="128"/>
       <c r="H36" s="25" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A37" s="225"/>
-      <c r="B37" s="226"/>
-      <c r="C37" s="177"/>
-      <c r="D37" s="173"/>
-      <c r="E37" s="173"/>
-      <c r="F37" s="220"/>
-      <c r="G37" s="175"/>
+    <row r="37" spans="1:8" ht="32">
+      <c r="A37" s="115"/>
+      <c r="B37" s="116"/>
+      <c r="C37" s="114"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="129"/>
       <c r="H37" s="25" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="162" x14ac:dyDescent="0.3">
-      <c r="A38" s="225"/>
-      <c r="B38" s="225" t="s">
+    <row r="38" spans="1:8" ht="192">
+      <c r="A38" s="115"/>
+      <c r="B38" s="115" t="s">
         <v>223</v>
       </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="123"/>
-      <c r="E38" s="123"/>
-      <c r="F38" s="125"/>
-      <c r="G38" s="122" t="s">
+      <c r="C38" s="97"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="96" t="s">
         <v>226</v>
       </c>
-      <c r="H38" s="122" t="s">
+      <c r="H38" s="96" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="226"/>
-      <c r="B39" s="226"/>
-      <c r="C39" s="124"/>
-      <c r="D39" s="123"/>
-      <c r="E39" s="123"/>
-      <c r="F39" s="125"/>
-      <c r="G39" s="122"/>
-      <c r="H39" s="122" t="s">
+    <row r="39" spans="1:8" ht="34.5" customHeight="1">
+      <c r="A39" s="116"/>
+      <c r="B39" s="116"/>
+      <c r="C39" s="97"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="96"/>
+      <c r="H39" s="96" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="240" t="s">
+    <row r="40" spans="1:8" ht="58.5" customHeight="1">
+      <c r="A40" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="241"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="126" t="s">
+      <c r="B40" s="190"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E40" s="126" t="s">
+      <c r="E40" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F40" s="126" t="s">
+      <c r="F40" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G40" s="127" t="s">
+      <c r="G40" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="H40" s="47" t="s">
+      <c r="H40" s="40" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="191" t="s">
+    <row r="41" spans="1:8" ht="124.5" customHeight="1">
+      <c r="A41" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="191" t="s">
+      <c r="B41" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="192" t="s">
+      <c r="C41" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="72" t="s">
+      <c r="D41" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="172" t="s">
+      <c r="E41" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="F41" s="172" t="s">
+      <c r="F41" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="193" t="s">
+      <c r="G41" s="164" t="s">
         <v>142</v>
       </c>
-      <c r="H41" s="194" t="s">
+      <c r="H41" s="165" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="141" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="191"/>
-      <c r="B42" s="191"/>
-      <c r="C42" s="192"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="195"/>
-      <c r="F42" s="195"/>
-      <c r="G42" s="193"/>
-      <c r="H42" s="194"/>
-    </row>
-    <row r="43" spans="1:8" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="191"/>
-      <c r="B43" s="47" t="s">
+    <row r="42" spans="1:8" ht="141" customHeight="1">
+      <c r="A42" s="163"/>
+      <c r="B42" s="163"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="164"/>
+      <c r="H42" s="165"/>
+    </row>
+    <row r="43" spans="1:8" ht="285.75" customHeight="1">
+      <c r="A43" s="163"/>
+      <c r="B43" s="40" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="17"/>
-      <c r="D43" s="72" t="s">
+      <c r="D43" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E43" s="173"/>
-      <c r="F43" s="173"/>
-      <c r="G43" s="193"/>
-      <c r="H43" s="40" t="s">
+      <c r="E43" s="124"/>
+      <c r="F43" s="124"/>
+      <c r="G43" s="164"/>
+      <c r="H43" s="36" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="191"/>
-      <c r="B44" s="80" t="s">
+    <row r="44" spans="1:8" ht="36.75" customHeight="1">
+      <c r="A44" s="163"/>
+      <c r="B44" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="196"/>
-      <c r="D44" s="72"/>
+      <c r="C44" s="166"/>
+      <c r="D44" s="26"/>
       <c r="E44"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="193"/>
-      <c r="H44" s="189" t="s">
+      <c r="F44" s="26"/>
+      <c r="G44" s="164"/>
+      <c r="H44" s="161" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="191"/>
-      <c r="B45" s="47" t="s">
+    <row r="45" spans="1:8" ht="78" customHeight="1">
+      <c r="A45" s="163"/>
+      <c r="B45" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="C45" s="196"/>
-      <c r="D45" s="72" t="s">
+      <c r="C45" s="166"/>
+      <c r="D45" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E45" s="72" t="s">
+      <c r="E45" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F45" s="72" t="s">
+      <c r="F45" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G45" s="193"/>
-      <c r="H45" s="190"/>
-    </row>
-    <row r="46" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="191"/>
-      <c r="B46" s="80" t="s">
+      <c r="G45" s="164"/>
+      <c r="H45" s="162"/>
+    </row>
+    <row r="46" spans="1:8" ht="50.25" customHeight="1">
+      <c r="A46" s="163"/>
+      <c r="B46" s="54" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="17"/>
-      <c r="D46" s="72" t="s">
+      <c r="D46" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E46" s="72" t="s">
+      <c r="E46" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F46" s="72" t="s">
+      <c r="F46" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G46" s="193"/>
-      <c r="H46" s="55" t="s">
+      <c r="G46" s="164"/>
+      <c r="H46" s="47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="136.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="209" t="s">
+    <row r="47" spans="1:8" ht="136.5" customHeight="1">
+      <c r="A47" s="158" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="80" t="s">
+      <c r="B47" s="54" t="s">
         <v>54</v>
       </c>
       <c r="C47" s="17"/>
-      <c r="D47" s="72" t="s">
+      <c r="D47" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E47" s="72" t="s">
+      <c r="E47" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F47" s="72" t="s">
+      <c r="F47" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G47" s="79" t="s">
+      <c r="G47" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="H47" s="137" t="s">
+      <c r="H47" s="105" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="210"/>
-      <c r="B48" s="213" t="s">
+    <row r="48" spans="1:8" ht="285.75" customHeight="1">
+      <c r="A48" s="159"/>
+      <c r="B48" s="138" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="172" t="s">
+      <c r="C48" s="38"/>
+      <c r="D48" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="187" t="s">
+      <c r="E48" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="F48" s="187" t="s">
+      <c r="F48" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="G48" s="75" t="s">
+      <c r="G48" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="H48" s="138" t="s">
+      <c r="H48" s="106" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="270" x14ac:dyDescent="0.3">
-      <c r="A49" s="210"/>
-      <c r="B49" s="214"/>
-      <c r="C49" s="73"/>
-      <c r="D49" s="195"/>
-      <c r="E49" s="187"/>
-      <c r="F49" s="187"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="139" t="s">
+    <row r="49" spans="1:8" ht="335">
+      <c r="A49" s="159"/>
+      <c r="B49" s="139"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="123"/>
+      <c r="E49" s="131"/>
+      <c r="F49" s="131"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="107" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="258" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="210"/>
-      <c r="B50" s="130"/>
-      <c r="C50" s="129"/>
-      <c r="D50" s="195"/>
-      <c r="E50" s="187"/>
-      <c r="F50" s="187"/>
-      <c r="G50" s="128"/>
-      <c r="H50" s="139" t="s">
+    <row r="50" spans="1:8" ht="258" customHeight="1">
+      <c r="A50" s="159"/>
+      <c r="B50" s="98"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="123"/>
+      <c r="E50" s="131"/>
+      <c r="F50" s="131"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="107" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="254.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="210"/>
-      <c r="B51" s="130"/>
-      <c r="C51" s="129"/>
-      <c r="D51" s="195"/>
-      <c r="E51" s="187"/>
-      <c r="F51" s="187"/>
-      <c r="G51" s="128"/>
-      <c r="H51" s="139" t="s">
+    <row r="51" spans="1:8" ht="254.25" customHeight="1">
+      <c r="A51" s="159"/>
+      <c r="B51" s="98"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="123"/>
+      <c r="E51" s="131"/>
+      <c r="F51" s="131"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="107" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="206.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="210"/>
-      <c r="B52" s="214" t="s">
+    <row r="52" spans="1:8" ht="206.25" customHeight="1">
+      <c r="A52" s="159"/>
+      <c r="B52" s="139" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="197"/>
-      <c r="D52" s="195"/>
-      <c r="E52" s="187"/>
-      <c r="F52" s="187"/>
-      <c r="G52" s="197"/>
-      <c r="H52" s="140" t="s">
+      <c r="C52" s="140"/>
+      <c r="D52" s="123"/>
+      <c r="E52" s="131"/>
+      <c r="F52" s="131"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="108" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="162" x14ac:dyDescent="0.3">
-      <c r="A53" s="210"/>
-      <c r="B53" s="214"/>
-      <c r="C53" s="198"/>
-      <c r="D53" s="195"/>
-      <c r="E53" s="187"/>
-      <c r="F53" s="187"/>
-      <c r="G53" s="199"/>
-      <c r="H53" s="140" t="s">
+    <row r="53" spans="1:8" ht="192">
+      <c r="A53" s="159"/>
+      <c r="B53" s="139"/>
+      <c r="C53" s="141"/>
+      <c r="D53" s="123"/>
+      <c r="E53" s="131"/>
+      <c r="F53" s="131"/>
+      <c r="G53" s="148"/>
+      <c r="H53" s="108" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="210"/>
-      <c r="B54" s="80" t="s">
+    <row r="54" spans="1:8" ht="16">
+      <c r="A54" s="159"/>
+      <c r="B54" s="54" t="s">
         <v>72</v>
       </c>
       <c r="C54" s="17"/>
-      <c r="D54" s="195"/>
-      <c r="E54" s="187"/>
-      <c r="F54" s="187"/>
-      <c r="G54" s="197"/>
+      <c r="D54" s="123"/>
+      <c r="E54" s="131"/>
+      <c r="F54" s="131"/>
+      <c r="G54" s="140"/>
       <c r="H54" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="210"/>
-      <c r="B55" s="80" t="s">
+    <row r="55" spans="1:8" ht="16">
+      <c r="A55" s="159"/>
+      <c r="B55" s="54" t="s">
         <v>73</v>
       </c>
       <c r="C55" s="17"/>
-      <c r="D55" s="195"/>
-      <c r="E55" s="187"/>
-      <c r="F55" s="187"/>
-      <c r="G55" s="198"/>
+      <c r="D55" s="123"/>
+      <c r="E55" s="131"/>
+      <c r="F55" s="131"/>
+      <c r="G55" s="141"/>
       <c r="H55" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="210"/>
-      <c r="B56" s="80" t="s">
+    <row r="56" spans="1:8" ht="16">
+      <c r="A56" s="159"/>
+      <c r="B56" s="54" t="s">
         <v>74</v>
       </c>
       <c r="C56" s="17"/>
-      <c r="D56" s="195"/>
-      <c r="E56" s="187"/>
-      <c r="F56" s="187"/>
-      <c r="G56" s="198"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="131"/>
+      <c r="F56" s="131"/>
+      <c r="G56" s="141"/>
       <c r="H56" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="210"/>
-      <c r="B57" s="80" t="s">
+    <row r="57" spans="1:8" ht="16">
+      <c r="A57" s="159"/>
+      <c r="B57" s="54" t="s">
         <v>75</v>
       </c>
       <c r="C57" s="17"/>
-      <c r="D57" s="195"/>
-      <c r="E57" s="187"/>
-      <c r="F57" s="187"/>
-      <c r="G57" s="198"/>
+      <c r="D57" s="123"/>
+      <c r="E57" s="131"/>
+      <c r="F57" s="131"/>
+      <c r="G57" s="141"/>
       <c r="H57" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="210"/>
-      <c r="B58" s="80" t="s">
+    <row r="58" spans="1:8" ht="16">
+      <c r="A58" s="159"/>
+      <c r="B58" s="54" t="s">
         <v>76</v>
       </c>
       <c r="C58" s="17"/>
-      <c r="D58" s="195"/>
-      <c r="E58" s="187"/>
-      <c r="F58" s="187"/>
-      <c r="G58" s="198"/>
+      <c r="D58" s="123"/>
+      <c r="E58" s="131"/>
+      <c r="F58" s="131"/>
+      <c r="G58" s="141"/>
       <c r="H58" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="210"/>
-      <c r="B59" s="80" t="s">
+    <row r="59" spans="1:8" ht="16">
+      <c r="A59" s="159"/>
+      <c r="B59" s="54" t="s">
         <v>77</v>
       </c>
       <c r="C59" s="17"/>
-      <c r="D59" s="195"/>
-      <c r="E59" s="187"/>
-      <c r="F59" s="187"/>
-      <c r="G59" s="198"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="131"/>
+      <c r="F59" s="131"/>
+      <c r="G59" s="141"/>
       <c r="H59" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="210"/>
-      <c r="B60" s="80" t="s">
+    <row r="60" spans="1:8" ht="16">
+      <c r="A60" s="159"/>
+      <c r="B60" s="54" t="s">
         <v>78</v>
       </c>
       <c r="C60" s="17"/>
-      <c r="D60" s="195"/>
-      <c r="E60" s="187"/>
-      <c r="F60" s="187"/>
-      <c r="G60" s="198"/>
+      <c r="D60" s="123"/>
+      <c r="E60" s="131"/>
+      <c r="F60" s="131"/>
+      <c r="G60" s="141"/>
       <c r="H60" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="210"/>
-      <c r="B61" s="80" t="s">
+    <row r="61" spans="1:8" ht="16">
+      <c r="A61" s="159"/>
+      <c r="B61" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="17"/>
-      <c r="D61" s="195"/>
-      <c r="E61" s="187"/>
-      <c r="F61" s="187"/>
-      <c r="G61" s="198"/>
+      <c r="D61" s="123"/>
+      <c r="E61" s="131"/>
+      <c r="F61" s="131"/>
+      <c r="G61" s="141"/>
       <c r="H61" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="210"/>
-      <c r="B62" s="80" t="s">
+    <row r="62" spans="1:8" ht="16">
+      <c r="A62" s="159"/>
+      <c r="B62" s="54" t="s">
         <v>90</v>
       </c>
       <c r="C62" s="17"/>
-      <c r="D62" s="195"/>
-      <c r="E62" s="187"/>
-      <c r="F62" s="187"/>
-      <c r="G62" s="198"/>
+      <c r="D62" s="123"/>
+      <c r="E62" s="131"/>
+      <c r="F62" s="131"/>
+      <c r="G62" s="141"/>
       <c r="H62" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="210"/>
-      <c r="B63" s="80" t="s">
+    <row r="63" spans="1:8" ht="18" customHeight="1">
+      <c r="A63" s="159"/>
+      <c r="B63" s="54" t="s">
         <v>88</v>
       </c>
       <c r="C63" s="17"/>
-      <c r="D63" s="195"/>
-      <c r="E63" s="187"/>
-      <c r="F63" s="187"/>
-      <c r="G63" s="198"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="131"/>
+      <c r="F63" s="131"/>
+      <c r="G63" s="141"/>
       <c r="H63" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A64" s="210"/>
-      <c r="B64" s="80" t="s">
+    <row r="64" spans="1:8" ht="32">
+      <c r="A64" s="159"/>
+      <c r="B64" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C64" s="17"/>
-      <c r="D64" s="195"/>
-      <c r="E64" s="187"/>
-      <c r="F64" s="187"/>
-      <c r="G64" s="198"/>
-      <c r="H64" s="57" t="s">
+      <c r="D64" s="123"/>
+      <c r="E64" s="131"/>
+      <c r="F64" s="131"/>
+      <c r="G64" s="141"/>
+      <c r="H64" s="49" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="210"/>
-      <c r="B65" s="80" t="s">
+    <row r="65" spans="1:8" ht="39.75" customHeight="1">
+      <c r="A65" s="159"/>
+      <c r="B65" s="54" t="s">
         <v>127</v>
       </c>
       <c r="C65" s="17"/>
-      <c r="D65" s="195"/>
-      <c r="E65" s="187"/>
-      <c r="F65" s="187"/>
-      <c r="G65" s="199"/>
-      <c r="H65" s="57" t="s">
+      <c r="D65" s="123"/>
+      <c r="E65" s="131"/>
+      <c r="F65" s="131"/>
+      <c r="G65" s="148"/>
+      <c r="H65" s="49" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="24.75" x14ac:dyDescent="0.3">
-      <c r="A66" s="210"/>
-      <c r="B66" s="52" t="s">
+    <row r="66" spans="1:8" ht="30">
+      <c r="A66" s="159"/>
+      <c r="B66" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C66" s="45" t="s">
+      <c r="C66" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="D66" s="72" t="s">
+      <c r="D66" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E66" s="72" t="s">
+      <c r="E66" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="72" t="s">
+      <c r="F66" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G66" s="82"/>
-      <c r="H66" s="41" t="s">
+      <c r="G66" s="31"/>
+      <c r="H66" s="37" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="210"/>
-      <c r="B67" s="80" t="s">
+    <row r="67" spans="1:8" ht="44.25" customHeight="1">
+      <c r="A67" s="159"/>
+      <c r="B67" s="54" t="s">
         <v>79</v>
       </c>
       <c r="C67" s="17"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="82"/>
-      <c r="H67" s="57" t="s">
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="49" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="210"/>
-      <c r="B68" s="80" t="s">
+    <row r="68" spans="1:8" ht="44.25" customHeight="1">
+      <c r="A68" s="159"/>
+      <c r="B68" s="54" t="s">
         <v>89</v>
       </c>
       <c r="C68" s="17"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
-      <c r="G68" s="82"/>
-      <c r="H68" s="57" t="s">
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="31"/>
+      <c r="H68" s="49" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="A69" s="210"/>
-      <c r="B69" s="80" t="s">
+    <row r="69" spans="1:8" ht="32">
+      <c r="A69" s="159"/>
+      <c r="B69" s="54" t="s">
         <v>56</v>
       </c>
       <c r="C69" s="17"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="82"/>
-      <c r="H69" s="56" t="s">
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="48" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="24.75" x14ac:dyDescent="0.3">
-      <c r="A70" s="210"/>
-      <c r="B70" s="80" t="s">
+    <row r="70" spans="1:8" ht="30">
+      <c r="A70" s="159"/>
+      <c r="B70" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="C70" s="82"/>
-      <c r="D70" s="72" t="s">
+      <c r="C70" s="31"/>
+      <c r="D70" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E70" s="72" t="s">
+      <c r="E70" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F70" s="72" t="s">
+      <c r="F70" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G70" s="82"/>
-      <c r="H70" s="56" t="s">
+      <c r="G70" s="31"/>
+      <c r="H70" s="48" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:8" s="39" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="211"/>
-      <c r="B71" s="80" t="s">
+    <row r="71" spans="1:8" s="35" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A71" s="160"/>
+      <c r="B71" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="45" t="s">
+      <c r="C71" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="D71" s="72" t="s">
+      <c r="D71" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E71" s="72" t="s">
+      <c r="E71" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="F71" s="72" t="s">
+      <c r="F71" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G71" s="84"/>
-      <c r="H71" s="58" t="s">
+      <c r="G71" s="28"/>
+      <c r="H71" s="50" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="203" t="s">
+    <row r="72" spans="1:8" ht="27" customHeight="1">
+      <c r="A72" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="204"/>
-      <c r="C72" s="192"/>
-      <c r="D72" s="187" t="s">
+      <c r="B72" s="154"/>
+      <c r="C72" s="136"/>
+      <c r="D72" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E72" s="187" t="s">
+      <c r="E72" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="187" t="s">
+      <c r="F72" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="G72" s="200" t="s">
+      <c r="G72" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="H72" s="83" t="s">
+      <c r="H72" s="43" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="205"/>
-      <c r="B73" s="206"/>
-      <c r="C73" s="192"/>
-      <c r="D73" s="187"/>
-      <c r="E73" s="187"/>
-      <c r="F73" s="187"/>
-      <c r="G73" s="200"/>
+    <row r="73" spans="1:8" ht="27" customHeight="1">
+      <c r="A73" s="155"/>
+      <c r="B73" s="143"/>
+      <c r="C73" s="136"/>
+      <c r="D73" s="131"/>
+      <c r="E73" s="131"/>
+      <c r="F73" s="131"/>
+      <c r="G73" s="133"/>
       <c r="H73" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="205"/>
-      <c r="B74" s="206"/>
-      <c r="C74" s="192"/>
-      <c r="D74" s="187"/>
-      <c r="E74" s="187"/>
-      <c r="F74" s="187"/>
-      <c r="G74" s="200"/>
-      <c r="H74" s="83" t="s">
+    <row r="74" spans="1:8" ht="27" customHeight="1">
+      <c r="A74" s="155"/>
+      <c r="B74" s="143"/>
+      <c r="C74" s="136"/>
+      <c r="D74" s="131"/>
+      <c r="E74" s="131"/>
+      <c r="F74" s="131"/>
+      <c r="G74" s="133"/>
+      <c r="H74" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="205"/>
-      <c r="B75" s="206"/>
-      <c r="C75" s="192"/>
-      <c r="D75" s="187"/>
-      <c r="E75" s="187"/>
-      <c r="F75" s="187"/>
-      <c r="G75" s="200"/>
+    <row r="75" spans="1:8" ht="27" customHeight="1">
+      <c r="A75" s="155"/>
+      <c r="B75" s="143"/>
+      <c r="C75" s="136"/>
+      <c r="D75" s="131"/>
+      <c r="E75" s="131"/>
+      <c r="F75" s="131"/>
+      <c r="G75" s="133"/>
       <c r="H75" s="18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="205"/>
-      <c r="B76" s="206"/>
-      <c r="C76" s="192"/>
-      <c r="D76" s="187"/>
-      <c r="E76" s="187"/>
-      <c r="F76" s="187"/>
-      <c r="G76" s="200"/>
-      <c r="H76" s="83" t="s">
+    <row r="76" spans="1:8" ht="27" customHeight="1">
+      <c r="A76" s="155"/>
+      <c r="B76" s="143"/>
+      <c r="C76" s="136"/>
+      <c r="D76" s="131"/>
+      <c r="E76" s="131"/>
+      <c r="F76" s="131"/>
+      <c r="G76" s="133"/>
+      <c r="H76" s="43" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="205"/>
-      <c r="B77" s="206"/>
-      <c r="C77" s="192"/>
-      <c r="D77" s="187"/>
-      <c r="E77" s="187"/>
-      <c r="F77" s="187"/>
-      <c r="G77" s="200"/>
+    <row r="77" spans="1:8" ht="27" customHeight="1">
+      <c r="A77" s="155"/>
+      <c r="B77" s="143"/>
+      <c r="C77" s="136"/>
+      <c r="D77" s="131"/>
+      <c r="E77" s="131"/>
+      <c r="F77" s="131"/>
+      <c r="G77" s="133"/>
       <c r="H77" s="18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="207"/>
-      <c r="B78" s="208"/>
-      <c r="C78" s="192"/>
-      <c r="D78" s="187"/>
-      <c r="E78" s="187"/>
-      <c r="F78" s="187"/>
-      <c r="G78" s="200"/>
-      <c r="H78" s="83" t="s">
+    <row r="78" spans="1:8" ht="27" customHeight="1">
+      <c r="A78" s="156"/>
+      <c r="B78" s="157"/>
+      <c r="C78" s="136"/>
+      <c r="D78" s="131"/>
+      <c r="E78" s="131"/>
+      <c r="F78" s="131"/>
+      <c r="G78" s="133"/>
+      <c r="H78" s="43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="240" t="s">
+    <row r="79" spans="1:8" ht="100.5" customHeight="1">
+      <c r="A79" s="189" t="s">
         <v>240</v>
       </c>
-      <c r="B79" s="241"/>
-      <c r="C79" s="143"/>
-      <c r="D79" s="142" t="s">
+      <c r="B79" s="190"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E79" s="142" t="s">
+      <c r="E79" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F79" s="142" t="s">
+      <c r="F79" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G79" s="145" t="s">
+      <c r="G79" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="H79" s="146" t="s">
+      <c r="H79" s="43" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="54" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="180" t="s">
+    <row r="80" spans="1:8" ht="64" hidden="1">
+      <c r="A80" s="134" t="s">
         <v>64</v>
       </c>
-      <c r="B80" s="76"/>
+      <c r="B80" s="53"/>
       <c r="C80" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D80" s="72" t="s">
+      <c r="D80" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="E80" s="72" t="s">
+      <c r="E80" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="F80" s="72" t="s">
+      <c r="F80" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="G80" s="84" t="s">
+      <c r="G80" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H80" s="51" t="s">
+      <c r="H80" s="44" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A81" s="180"/>
-      <c r="B81" s="76" t="s">
+    <row r="81" spans="1:8" ht="64">
+      <c r="A81" s="134"/>
+      <c r="B81" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="C81" s="81"/>
-      <c r="D81" s="72" t="s">
+      <c r="C81" s="27"/>
+      <c r="D81" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E81" s="72" t="s">
+      <c r="E81" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="F81" s="72" t="s">
+      <c r="F81" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G81" s="84" t="s">
+      <c r="G81" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H81" s="51" t="s">
+      <c r="H81" s="44" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="54" x14ac:dyDescent="0.3">
-      <c r="A82" s="76" t="s">
+    <row r="82" spans="1:8" ht="64">
+      <c r="A82" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="B82" s="76" t="s">
+      <c r="B82" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C82" s="85" t="s">
+      <c r="C82" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="D82" s="72" t="s">
+      <c r="D82" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="E82" s="72" t="s">
+      <c r="E82" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F82" s="72" t="s">
+      <c r="F82" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="G82" s="84" t="s">
+      <c r="G82" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="H82" s="51" t="s">
+      <c r="H82" s="44" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="11" t="s">
         <v>50</v>
       </c>
       <c r="B83" s="10"/>
       <c r="C83" s="1"/>
     </row>
-    <row r="84" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="153" t="s">
+    <row r="84" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A84" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="201"/>
-      <c r="C84" s="155" t="s">
+      <c r="B84" s="150"/>
+      <c r="C84" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="D84" s="77" t="s">
+      <c r="D84" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="77"/>
-      <c r="F84" s="212" t="s">
+      <c r="E84" s="62"/>
+      <c r="F84" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="155" t="s">
+      <c r="G84" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="H84" s="155" t="s">
+      <c r="H84" s="147" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="154"/>
-      <c r="B85" s="202"/>
-      <c r="C85" s="155"/>
+    <row r="85" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A85" s="151"/>
+      <c r="B85" s="152"/>
+      <c r="C85" s="147"/>
       <c r="D85" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F85" s="212"/>
-      <c r="G85" s="155"/>
-      <c r="H85" s="155"/>
-    </row>
-    <row r="86" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="172" t="s">
+      <c r="F85" s="146"/>
+      <c r="G85" s="147"/>
+      <c r="H85" s="147"/>
+    </row>
+    <row r="86" spans="1:8" ht="91.5" customHeight="1">
+      <c r="A86" s="122" t="s">
         <v>61</v>
       </c>
       <c r="B86" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="169" t="s">
+      <c r="C86" s="144" t="s">
         <v>82</v>
       </c>
       <c r="D86" s="22" t="s">
@@ -11317,308 +11199,308 @@
       <c r="F86" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G86" s="174" t="s">
+      <c r="G86" s="127" t="s">
         <v>83</v>
       </c>
       <c r="H86" s="21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="124.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="195"/>
-      <c r="B87" s="74" t="s">
+    <row r="87" spans="1:8" ht="124.5" customHeight="1">
+      <c r="A87" s="123"/>
+      <c r="B87" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C87" s="171"/>
-      <c r="D87" s="74" t="s">
+      <c r="C87" s="145"/>
+      <c r="D87" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E87" s="74" t="s">
+      <c r="E87" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F87" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G87" s="175"/>
+      <c r="G87" s="129"/>
       <c r="H87" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="173"/>
+    <row r="88" spans="1:8" ht="77.25" customHeight="1">
+      <c r="A88" s="124"/>
       <c r="B88" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C88" s="82" t="s">
+      <c r="C88" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="D88" s="72" t="s">
+      <c r="D88" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E88" s="72" t="s">
+      <c r="E88" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="F88" s="72" t="s">
+      <c r="F88" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="G88" s="84" t="s">
+      <c r="G88" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H88" s="84" t="s">
+      <c r="H88" s="28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="191.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="72" t="s">
+    <row r="89" spans="1:8" ht="191.25" customHeight="1">
+      <c r="A89" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B89" s="72"/>
-      <c r="C89" s="81"/>
-      <c r="D89" s="72"/>
-      <c r="E89" s="72"/>
-      <c r="F89" s="72"/>
-      <c r="G89" s="60" t="s">
+      <c r="B89" s="26"/>
+      <c r="C89" s="27"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="H89" s="84" t="s">
+      <c r="H89" s="28" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="G113" s="2"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="G115" s="2"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="G116" s="2"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="G118" s="2"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="G119" s="2"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="G120" s="2"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="G121" s="2"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="G122" s="2"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="G124" s="2"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="G125" s="2"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="G126" s="2"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="G127" s="2"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="G128" s="2"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="G129" s="2"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="G130" s="2"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="G131" s="2"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="G133" s="2"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="G134" s="2"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="G135" s="2"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="G136" s="2"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
       <c r="G137" s="2"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="G138" s="2"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="G139" s="2"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="G140" s="2"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="G141" s="2"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="G142" s="2"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="G143" s="2"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="G144" s="2"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -11626,6 +11508,83 @@
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B31"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G46"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="G54:G65"/>
+    <mergeCell ref="A72:B78"/>
+    <mergeCell ref="C72:C78"/>
+    <mergeCell ref="D72:D78"/>
+    <mergeCell ref="E72:E78"/>
+    <mergeCell ref="F72:F78"/>
+    <mergeCell ref="G72:G78"/>
+    <mergeCell ref="A47:A71"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="D48:D65"/>
+    <mergeCell ref="E48:E65"/>
+    <mergeCell ref="F48:F65"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="C86:C87"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="F16:F17"/>
     <mergeCell ref="G30:G31"/>
@@ -11650,83 +11609,6 @@
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E21:E22"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="H84:H85"/>
-    <mergeCell ref="G54:G65"/>
-    <mergeCell ref="A72:B78"/>
-    <mergeCell ref="C72:C78"/>
-    <mergeCell ref="D72:D78"/>
-    <mergeCell ref="E72:E78"/>
-    <mergeCell ref="F72:F78"/>
-    <mergeCell ref="G72:G78"/>
-    <mergeCell ref="A47:A71"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="D48:D65"/>
-    <mergeCell ref="E48:E65"/>
-    <mergeCell ref="F48:F65"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G46"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="A32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B31"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="A7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="D7:D11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11749,21 +11631,21 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="244"/>
-      <c r="B1" s="244"/>
-      <c r="C1" s="244"/>
-      <c r="D1" s="244"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
+      <c r="A1" s="203"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="20"/>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="20"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -11785,144 +11667,133 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="6.625" style="64" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" style="64" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="112.375" style="64" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="64"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="112.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="250" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="204" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="250"/>
-      <c r="C1" s="250" t="s">
+      <c r="B1" s="204"/>
+      <c r="C1" s="204" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
+    <row r="2" spans="1:3" ht="18">
+      <c r="A2" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="250"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="251" t="s">
+      <c r="C2" s="204"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="205" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="252" t="s">
+      <c r="B3" s="206" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="208" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="251"/>
-      <c r="B4" s="253"/>
-      <c r="C4" s="246"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="249" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="205"/>
+      <c r="B4" s="207"/>
+      <c r="C4" s="208"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="209" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="249" t="s">
+      <c r="B5" s="209" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="246" t="s">
+      <c r="C5" s="208" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="249"/>
-      <c r="B6" s="249"/>
-      <c r="C6" s="246"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="249" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="209"/>
+      <c r="B6" s="209"/>
+      <c r="C6" s="208"/>
+    </row>
+    <row r="7" spans="1:3" ht="18">
+      <c r="A7" s="209" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="246" t="s">
+      <c r="C7" s="208" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="249"/>
-      <c r="B8" s="67" t="s">
+    <row r="8" spans="1:3" ht="18">
+      <c r="A8" s="209"/>
+      <c r="B8" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="246"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="247" t="s">
+      <c r="C8" s="208"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="211" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="246" t="s">
+      <c r="C9" s="208" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="247"/>
-      <c r="B10" s="247"/>
-      <c r="C10" s="246"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="248" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="211"/>
+      <c r="B10" s="211"/>
+      <c r="C10" s="208"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="212" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="248" t="s">
+      <c r="B11" s="212" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="246" t="s">
+      <c r="C11" s="208" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="248"/>
-      <c r="B12" s="248"/>
-      <c r="C12" s="246"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="245" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="212"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="208"/>
+    </row>
+    <row r="13" spans="1:3" ht="18">
+      <c r="A13" s="210" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="246" t="s">
+      <c r="C13" s="208" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="245"/>
-      <c r="B14" s="69" t="s">
+    <row r="14" spans="1:3" ht="18">
+      <c r="A14" s="210"/>
+      <c r="B14" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="246"/>
+      <c r="C14" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="A9:A10"/>
@@ -11931,6 +11802,16 @@
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/uploads_local/사모_판매대본_한국투자반도체&코스닥일반사모투자신탁.xlsx
+++ b/data/uploads_local/사모_판매대본_한국투자반도체&코스닥일반사모투자신탁.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a114384/Desktop/2.KISAI/펀드 불완전판매/data/uploads_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089FA34F-0AD9-244D-9CAB-90FA45C42D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A54E0E2-7EFF-7B4F-9150-0C0A0DD7E7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="760" windowWidth="17280" windowHeight="20440" activeTab="1" xr2:uid="{27046729-DC8E-4EC9-9EBE-9FEAE0333B25}"/>
+    <workbookView xWindow="1280" yWindow="760" windowWidth="32000" windowHeight="20440" activeTab="1" xr2:uid="{27046729-DC8E-4EC9-9EBE-9FEAE0333B25}"/>
   </bookViews>
   <sheets>
     <sheet name="(내점) 투자자정보(26.01.02)" sheetId="79" r:id="rId1"/>
@@ -6449,7 +6449,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6786,15 +6786,174 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6810,258 +6969,120 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -7074,25 +7095,13 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7828,15 +7837,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="175" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
     </row>
     <row r="2" spans="1:7">
       <c r="G2" s="9" t="s">
@@ -7856,38 +7865,38 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:7" s="66" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="B5" s="147" t="s">
+      <c r="B5" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="182" t="s">
+      <c r="C5" s="177" t="s">
         <v>152</v>
       </c>
-      <c r="D5" s="182" t="s">
+      <c r="D5" s="177" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="182"/>
-      <c r="F5" s="147" t="s">
+      <c r="E5" s="177"/>
+      <c r="F5" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="147" t="s">
+      <c r="G5" s="115" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="66" customFormat="1" ht="45">
-      <c r="A6" s="151"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="182"/>
+      <c r="A6" s="141"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="177"/>
       <c r="D6" s="67" t="s">
         <v>154</v>
       </c>
       <c r="E6" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="F6" s="147"/>
-      <c r="G6" s="147"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
     </row>
     <row r="7" spans="1:7" ht="58.5" customHeight="1">
       <c r="A7" s="68" t="s">
@@ -7909,22 +7918,22 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="58.5" customHeight="1">
-      <c r="A8" s="183" t="s">
+      <c r="A8" s="178" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="185" t="s">
+      <c r="B8" s="180" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="187" t="s">
+      <c r="C8" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="187" t="s">
+      <c r="D8" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="187" t="s">
+      <c r="E8" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="178" t="s">
+      <c r="F8" s="173" t="s">
         <v>159</v>
       </c>
       <c r="G8" s="71" t="s">
@@ -7932,12 +7941,12 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="58.5" customHeight="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="186"/>
-      <c r="C9" s="188"/>
-      <c r="D9" s="188"/>
-      <c r="E9" s="188"/>
-      <c r="F9" s="179"/>
+      <c r="A9" s="179"/>
+      <c r="B9" s="181"/>
+      <c r="C9" s="183"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="183"/>
+      <c r="F9" s="174"/>
       <c r="G9" s="72" t="s">
         <v>161</v>
       </c>
@@ -7966,7 +7975,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A11" s="174" t="s">
+      <c r="A11" s="184" t="s">
         <v>165</v>
       </c>
       <c r="B11" s="75" t="s">
@@ -7977,7 +7986,7 @@
       </c>
       <c r="D11" s="76"/>
       <c r="E11" s="76"/>
-      <c r="F11" s="127" t="s">
+      <c r="F11" s="113" t="s">
         <v>167</v>
       </c>
       <c r="G11" s="77" t="s">
@@ -7985,7 +7994,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A12" s="175"/>
+      <c r="A12" s="185"/>
       <c r="B12" s="78" t="s">
         <v>169</v>
       </c>
@@ -7994,13 +8003,13 @@
         <v>5</v>
       </c>
       <c r="E12" s="79"/>
-      <c r="F12" s="128"/>
+      <c r="F12" s="166"/>
       <c r="G12" s="81" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="50.25" customHeight="1">
-      <c r="A13" s="176"/>
+      <c r="A13" s="186"/>
       <c r="B13" s="82" t="s">
         <v>170</v>
       </c>
@@ -8009,7 +8018,7 @@
       <c r="E13" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="129"/>
+      <c r="F13" s="114"/>
       <c r="G13" s="85" t="s">
         <v>171</v>
       </c>
@@ -8018,7 +8027,7 @@
       <c r="A14" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="144" t="s">
+      <c r="B14" s="152" t="s">
         <v>173</v>
       </c>
       <c r="C14" s="26" t="s">
@@ -8038,20 +8047,20 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="89.25" customHeight="1">
-      <c r="A15" s="174" t="s">
+      <c r="A15" s="184" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="177"/>
-      <c r="C15" s="122" t="s">
+      <c r="B15" s="187"/>
+      <c r="C15" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="122" t="s">
+      <c r="D15" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="122" t="s">
+      <c r="E15" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="127" t="s">
+      <c r="F15" s="113" t="s">
         <v>176</v>
       </c>
       <c r="G15" s="74" t="s">
@@ -8059,43 +8068,43 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A16" s="176"/>
-      <c r="B16" s="145"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="129"/>
+      <c r="A16" s="186"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="133"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="114"/>
       <c r="G16" s="87" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="60" customHeight="1">
-      <c r="A17" s="122" t="s">
+      <c r="A17" s="131" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="112" t="s">
+      <c r="B17" s="158" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="122" t="s">
+      <c r="C17" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="172"/>
-      <c r="E17" s="172"/>
-      <c r="F17" s="127" t="s">
+      <c r="D17" s="188"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="113" t="s">
         <v>180</v>
       </c>
-      <c r="G17" s="127" t="s">
+      <c r="G17" s="113" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="90" customHeight="1">
-      <c r="A18" s="124"/>
-      <c r="B18" s="114"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
+      <c r="A18" s="133"/>
+      <c r="B18" s="159"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="189"/>
+      <c r="E18" s="189"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
     </row>
     <row r="35" spans="6:6">
       <c r="F35" s="2"/>
@@ -8222,6 +8231,21 @@
     <filterColumn colId="0" showButton="0"/>
   </autoFilter>
   <mergeCells count="28">
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:A6"/>
@@ -8235,21 +8259,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -8271,7 +8280,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.83203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="27.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="5.83203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="5.5" style="1" customWidth="1"/>
@@ -8312,57 +8321,57 @@
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147" t="s">
+      <c r="B5" s="115"/>
+      <c r="C5" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="167" t="s">
+      <c r="E5" s="118" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="168"/>
-      <c r="G5" s="147" t="s">
+      <c r="F5" s="119"/>
+      <c r="G5" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="147" t="s">
+      <c r="H5" s="115" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A6" s="147"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="147"/>
-      <c r="D6" s="169"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="120"/>
       <c r="E6" s="90" t="s">
         <v>211</v>
       </c>
       <c r="F6" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="147"/>
-      <c r="H6" s="147"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
     </row>
     <row r="7" spans="1:8" ht="59.25" customHeight="1">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="136" t="s">
+      <c r="B7" s="116"/>
+      <c r="C7" s="128" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="131" t="s">
+      <c r="D7" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="131" t="s">
+      <c r="E7" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="132"/>
-      <c r="G7" s="137" t="s">
+      <c r="F7" s="157"/>
+      <c r="G7" s="117" t="s">
         <v>183</v>
       </c>
       <c r="H7" s="91" t="s">
@@ -8370,22 +8379,22 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="58.5" customHeight="1">
-      <c r="A8" s="134"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="137"/>
+      <c r="A8" s="116"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="128"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="157"/>
+      <c r="G8" s="117"/>
       <c r="H8" s="13" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="168" customHeight="1">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="B9" s="134"/>
+      <c r="B9" s="116"/>
       <c r="C9" s="27" t="s">
         <v>185</v>
       </c>
@@ -8399,24 +8408,24 @@
       <c r="G9" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="215" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="159.75" customHeight="1">
-      <c r="A10" s="134"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="136" t="s">
+      <c r="A10" s="116"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="128" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="131" t="s">
+      <c r="D10" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="131" t="s">
+      <c r="E10" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="132"/>
-      <c r="G10" s="133" t="s">
+      <c r="F10" s="157"/>
+      <c r="G10" s="138" t="s">
         <v>189</v>
       </c>
       <c r="H10" s="28" t="s">
@@ -8424,66 +8433,66 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A11" s="134"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="136"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="133"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="138"/>
       <c r="H11" s="92" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A12" s="134" t="s">
+      <c r="A12" s="116" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="134"/>
-      <c r="C12" s="130" t="s">
+      <c r="B12" s="116"/>
+      <c r="C12" s="122" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="131" t="s">
+      <c r="D12" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="131" t="s">
+      <c r="E12" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="132"/>
-      <c r="G12" s="137" t="s">
+      <c r="F12" s="157"/>
+      <c r="G12" s="117" t="s">
         <v>193</v>
       </c>
-      <c r="H12" s="137" t="s">
+      <c r="H12" s="117" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A13" s="134"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
+      <c r="A13" s="116"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="157"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
     </row>
     <row r="14" spans="1:8" ht="108" customHeight="1">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="124" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="171"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
-      <c r="F14" s="171"/>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="124"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="124"/>
     </row>
     <row r="15" spans="1:8" ht="58.5" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="B15" s="134"/>
+      <c r="B15" s="116"/>
       <c r="C15" s="88" t="s">
         <v>197</v>
       </c>
@@ -8500,53 +8509,53 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="96" customHeight="1">
-      <c r="A16" s="170" t="s">
+      <c r="A16" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="170"/>
-      <c r="C16" s="136" t="s">
+      <c r="B16" s="121"/>
+      <c r="C16" s="128" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="131" t="s">
+      <c r="D16" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="131" t="s">
+      <c r="E16" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="132"/>
-      <c r="G16" s="135"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="161"/>
       <c r="H16" s="15" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A17" s="170"/>
-      <c r="B17" s="170"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="135"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="123"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="161"/>
       <c r="H17" s="93" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="60" customHeight="1">
-      <c r="A18" s="170"/>
-      <c r="B18" s="170"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="135"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="161"/>
       <c r="H18" s="15" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="105.75" customHeight="1">
-      <c r="A19" s="170"/>
-      <c r="B19" s="170"/>
-      <c r="C19" s="130" t="s">
+      <c r="A19" s="121"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="122" t="s">
         <v>203</v>
       </c>
       <c r="D19" s="26" t="s">
@@ -8556,7 +8565,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="64"/>
-      <c r="G19" s="126" t="s">
+      <c r="G19" s="165" t="s">
         <v>204</v>
       </c>
       <c r="H19" s="16" t="s">
@@ -8564,9 +8573,9 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="93.75" customHeight="1">
-      <c r="A20" s="170"/>
-      <c r="B20" s="170"/>
-      <c r="C20" s="130"/>
+      <c r="A20" s="121"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="122"/>
       <c r="D20" s="26" t="s">
         <v>5</v>
       </c>
@@ -8574,46 +8583,46 @@
         <v>5</v>
       </c>
       <c r="F20" s="64"/>
-      <c r="G20" s="126"/>
+      <c r="G20" s="165"/>
       <c r="H20" s="15" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A21" s="142" t="s">
+      <c r="A21" s="160" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="143"/>
-      <c r="C21" s="112" t="s">
+      <c r="B21" s="146"/>
+      <c r="C21" s="158" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="122" t="s">
+      <c r="D21" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="122" t="s">
+      <c r="E21" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="120"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127" t="s">
+      <c r="F21" s="162"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A22" s="142"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="129"/>
-      <c r="H22" s="129"/>
-    </row>
-    <row r="23" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A23" s="118" t="s">
+      <c r="A22" s="160"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="159"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="163"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+    </row>
+    <row r="23" spans="1:8" ht="47" customHeight="1">
+      <c r="A23" s="216" t="s">
         <v>232</v>
       </c>
-      <c r="B23" s="119"/>
+      <c r="B23" s="217"/>
       <c r="C23" s="100"/>
       <c r="D23" s="101"/>
       <c r="E23" s="101"/>
@@ -8624,17 +8633,17 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="108" customHeight="1">
-      <c r="A24" s="117" t="s">
+      <c r="A24" s="170" t="s">
         <v>224</v>
       </c>
-      <c r="B24" s="117" t="s">
+      <c r="B24" s="170" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="112"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="127" t="s">
+      <c r="C24" s="158"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="113" t="s">
         <v>225</v>
       </c>
       <c r="H24" s="99" t="s">
@@ -8642,32 +8651,32 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A25" s="115"/>
-      <c r="B25" s="115"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="128"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="168"/>
+      <c r="C25" s="167"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="164"/>
+      <c r="G25" s="166"/>
       <c r="H25" s="25" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="32">
-      <c r="A26" s="115"/>
-      <c r="B26" s="116"/>
-      <c r="C26" s="114"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="129"/>
+      <c r="A26" s="168"/>
+      <c r="B26" s="169"/>
+      <c r="C26" s="159"/>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="163"/>
+      <c r="G26" s="114"/>
       <c r="H26" s="25" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="165" customHeight="1">
-      <c r="A27" s="115"/>
-      <c r="B27" s="115" t="s">
+      <c r="A27" s="168"/>
+      <c r="B27" s="168" t="s">
         <v>223</v>
       </c>
       <c r="C27" s="97"/>
@@ -8682,8 +8691,8 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A28" s="116"/>
-      <c r="B28" s="116"/>
+      <c r="A28" s="169"/>
+      <c r="B28" s="169"/>
       <c r="C28" s="97"/>
       <c r="D28" s="34"/>
       <c r="E28" s="34"/>
@@ -8694,10 +8703,10 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="58.5" customHeight="1">
-      <c r="A29" s="134" t="s">
+      <c r="A29" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="134"/>
+      <c r="B29" s="116"/>
       <c r="C29" s="33"/>
       <c r="D29" s="26" t="s">
         <v>0</v>
@@ -8711,48 +8720,48 @@
       <c r="G29" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="H29" s="213" t="s">
+      <c r="H29" s="112" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="124.5" customHeight="1">
-      <c r="A30" s="163" t="s">
+      <c r="A30" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="163" t="s">
+      <c r="B30" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="136" t="s">
+      <c r="C30" s="128" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="122" t="s">
+      <c r="E30" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="122" t="s">
+      <c r="F30" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="G30" s="164" t="s">
+      <c r="G30" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="H30" s="214" t="s">
+      <c r="H30" s="130" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="175" customHeight="1">
-      <c r="A31" s="163"/>
-      <c r="B31" s="163"/>
-      <c r="C31" s="136"/>
+      <c r="A31" s="127"/>
+      <c r="B31" s="127"/>
+      <c r="C31" s="128"/>
       <c r="D31" s="26"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="123"/>
-      <c r="G31" s="164"/>
-      <c r="H31" s="214"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="132"/>
+      <c r="G31" s="129"/>
+      <c r="H31" s="130"/>
     </row>
     <row r="32" spans="1:8" ht="285.75" customHeight="1">
-      <c r="A32" s="163"/>
+      <c r="A32" s="127"/>
       <c r="B32" s="40" t="s">
         <v>11</v>
       </c>
@@ -8760,33 +8769,33 @@
       <c r="D32" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="164"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="129"/>
       <c r="H32" s="36" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A33" s="163"/>
+      <c r="A33" s="127"/>
       <c r="B33" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="166"/>
+      <c r="C33" s="134"/>
       <c r="D33" s="26"/>
       <c r="E33"/>
       <c r="F33" s="26"/>
-      <c r="G33" s="164"/>
-      <c r="H33" s="161" t="s">
+      <c r="G33" s="129"/>
+      <c r="H33" s="125" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="78" customHeight="1">
-      <c r="A34" s="163"/>
+      <c r="A34" s="127"/>
       <c r="B34" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="166"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="26" t="s">
         <v>0</v>
       </c>
@@ -8796,11 +8805,11 @@
       <c r="F34" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G34" s="164"/>
-      <c r="H34" s="162"/>
+      <c r="G34" s="129"/>
+      <c r="H34" s="126"/>
     </row>
     <row r="35" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A35" s="163"/>
+      <c r="A35" s="127"/>
       <c r="B35" s="54" t="s">
         <v>12</v>
       </c>
@@ -8814,13 +8823,13 @@
       <c r="F35" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G35" s="164"/>
+      <c r="G35" s="129"/>
       <c r="H35" s="47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="153" customHeight="1">
-      <c r="A36" s="158">
+      <c r="A36" s="149">
         <v>2943</v>
       </c>
       <c r="B36" s="54" t="s">
@@ -8844,18 +8853,18 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="274.5" customHeight="1">
-      <c r="A37" s="159"/>
-      <c r="B37" s="138" t="s">
+      <c r="A37" s="150"/>
+      <c r="B37" s="155" t="s">
         <v>71</v>
       </c>
       <c r="C37" s="38"/>
-      <c r="D37" s="122" t="s">
+      <c r="D37" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="131" t="s">
+      <c r="E37" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="131" t="s">
+      <c r="F37" s="123" t="s">
         <v>70</v>
       </c>
       <c r="G37" s="41" t="s">
@@ -8866,237 +8875,237 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="298.5" customHeight="1">
-      <c r="A38" s="159"/>
-      <c r="B38" s="139"/>
+      <c r="A38" s="150"/>
+      <c r="B38" s="156"/>
       <c r="C38" s="38"/>
-      <c r="D38" s="123"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="131"/>
+      <c r="D38" s="132"/>
+      <c r="E38" s="123"/>
+      <c r="F38" s="123"/>
       <c r="G38" s="41"/>
       <c r="H38" s="107" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="224">
-      <c r="A39" s="159"/>
+      <c r="A39" s="150"/>
       <c r="B39" s="98"/>
       <c r="C39" s="38"/>
-      <c r="D39" s="123"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="131"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="123"/>
+      <c r="F39" s="123"/>
       <c r="G39" s="41"/>
       <c r="H39" s="107" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="273.75" customHeight="1">
-      <c r="A40" s="159"/>
+      <c r="A40" s="150"/>
       <c r="B40" s="98"/>
       <c r="C40" s="38"/>
-      <c r="D40" s="123"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="131"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="123"/>
       <c r="G40" s="41"/>
       <c r="H40" s="107" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="222" customHeight="1">
-      <c r="A41" s="159"/>
-      <c r="B41" s="139" t="s">
+      <c r="A41" s="150"/>
+      <c r="B41" s="156" t="s">
         <v>144</v>
       </c>
-      <c r="C41" s="140"/>
-      <c r="D41" s="123"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="140"/>
+      <c r="C41" s="135"/>
+      <c r="D41" s="132"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="135"/>
       <c r="H41" s="108" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="208">
-      <c r="A42" s="159"/>
-      <c r="B42" s="139"/>
-      <c r="C42" s="141"/>
-      <c r="D42" s="123"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="148"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="156"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="137"/>
       <c r="H42" s="108" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16">
-      <c r="A43" s="159"/>
+      <c r="A43" s="150"/>
       <c r="B43" s="54" t="s">
         <v>72</v>
       </c>
       <c r="C43" s="17"/>
-      <c r="D43" s="123"/>
-      <c r="E43" s="131"/>
-      <c r="F43" s="131"/>
-      <c r="G43" s="140"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="123"/>
+      <c r="F43" s="123"/>
+      <c r="G43" s="135"/>
       <c r="H43" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16">
-      <c r="A44" s="159"/>
+      <c r="A44" s="150"/>
       <c r="B44" s="54" t="s">
         <v>73</v>
       </c>
       <c r="C44" s="17"/>
-      <c r="D44" s="123"/>
-      <c r="E44" s="131"/>
-      <c r="F44" s="131"/>
-      <c r="G44" s="141"/>
+      <c r="D44" s="132"/>
+      <c r="E44" s="123"/>
+      <c r="F44" s="123"/>
+      <c r="G44" s="136"/>
       <c r="H44" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="16">
-      <c r="A45" s="159"/>
+      <c r="A45" s="150"/>
       <c r="B45" s="54" t="s">
         <v>74</v>
       </c>
       <c r="C45" s="17"/>
-      <c r="D45" s="123"/>
-      <c r="E45" s="131"/>
-      <c r="F45" s="131"/>
-      <c r="G45" s="141"/>
+      <c r="D45" s="132"/>
+      <c r="E45" s="123"/>
+      <c r="F45" s="123"/>
+      <c r="G45" s="136"/>
       <c r="H45" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="16">
-      <c r="A46" s="159"/>
+      <c r="A46" s="150"/>
       <c r="B46" s="54" t="s">
         <v>75</v>
       </c>
       <c r="C46" s="17"/>
-      <c r="D46" s="123"/>
-      <c r="E46" s="131"/>
-      <c r="F46" s="131"/>
-      <c r="G46" s="141"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="123"/>
+      <c r="F46" s="123"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="16">
-      <c r="A47" s="159"/>
+      <c r="A47" s="150"/>
       <c r="B47" s="54" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="17"/>
-      <c r="D47" s="123"/>
-      <c r="E47" s="131"/>
-      <c r="F47" s="131"/>
-      <c r="G47" s="141"/>
+      <c r="D47" s="132"/>
+      <c r="E47" s="123"/>
+      <c r="F47" s="123"/>
+      <c r="G47" s="136"/>
       <c r="H47" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16">
-      <c r="A48" s="159"/>
+      <c r="A48" s="150"/>
       <c r="B48" s="54" t="s">
         <v>77</v>
       </c>
       <c r="C48" s="17"/>
-      <c r="D48" s="123"/>
-      <c r="E48" s="131"/>
-      <c r="F48" s="131"/>
-      <c r="G48" s="141"/>
+      <c r="D48" s="132"/>
+      <c r="E48" s="123"/>
+      <c r="F48" s="123"/>
+      <c r="G48" s="136"/>
       <c r="H48" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="16">
-      <c r="A49" s="159"/>
+      <c r="A49" s="150"/>
       <c r="B49" s="54" t="s">
         <v>78</v>
       </c>
       <c r="C49" s="17"/>
-      <c r="D49" s="123"/>
-      <c r="E49" s="131"/>
-      <c r="F49" s="131"/>
-      <c r="G49" s="141"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="123"/>
+      <c r="F49" s="123"/>
+      <c r="G49" s="136"/>
       <c r="H49" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="16">
-      <c r="A50" s="159"/>
+      <c r="A50" s="150"/>
       <c r="B50" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="17"/>
-      <c r="D50" s="123"/>
-      <c r="E50" s="131"/>
-      <c r="F50" s="131"/>
-      <c r="G50" s="141"/>
+      <c r="D50" s="132"/>
+      <c r="E50" s="123"/>
+      <c r="F50" s="123"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="16">
-      <c r="A51" s="159"/>
+      <c r="A51" s="150"/>
       <c r="B51" s="54" t="s">
         <v>90</v>
       </c>
       <c r="C51" s="17"/>
-      <c r="D51" s="123"/>
-      <c r="E51" s="131"/>
-      <c r="F51" s="131"/>
-      <c r="G51" s="141"/>
+      <c r="D51" s="132"/>
+      <c r="E51" s="123"/>
+      <c r="F51" s="123"/>
+      <c r="G51" s="136"/>
       <c r="H51" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="18" customHeight="1">
-      <c r="A52" s="159"/>
+      <c r="A52" s="150"/>
       <c r="B52" s="54" t="s">
         <v>88</v>
       </c>
       <c r="C52" s="17"/>
-      <c r="D52" s="123"/>
-      <c r="E52" s="131"/>
-      <c r="F52" s="131"/>
-      <c r="G52" s="141"/>
+      <c r="D52" s="132"/>
+      <c r="E52" s="123"/>
+      <c r="F52" s="123"/>
+      <c r="G52" s="136"/>
       <c r="H52" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="32">
-      <c r="A53" s="159"/>
+      <c r="A53" s="150"/>
       <c r="B53" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C53" s="17"/>
-      <c r="D53" s="123"/>
-      <c r="E53" s="131"/>
-      <c r="F53" s="131"/>
-      <c r="G53" s="141"/>
+      <c r="D53" s="132"/>
+      <c r="E53" s="123"/>
+      <c r="F53" s="123"/>
+      <c r="G53" s="136"/>
       <c r="H53" s="49" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A54" s="159"/>
+      <c r="A54" s="150"/>
       <c r="B54" s="54" t="s">
         <v>127</v>
       </c>
       <c r="C54" s="17"/>
-      <c r="D54" s="123"/>
-      <c r="E54" s="131"/>
-      <c r="F54" s="131"/>
-      <c r="G54" s="148"/>
+      <c r="D54" s="132"/>
+      <c r="E54" s="123"/>
+      <c r="F54" s="123"/>
+      <c r="G54" s="137"/>
       <c r="H54" s="49" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="48">
-      <c r="A55" s="159"/>
+      <c r="A55" s="150"/>
       <c r="B55" s="45" t="s">
         <v>105</v>
       </c>
@@ -9118,7 +9127,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="44.25" customHeight="1">
-      <c r="A56" s="159"/>
+      <c r="A56" s="150"/>
       <c r="B56" s="54" t="s">
         <v>79</v>
       </c>
@@ -9132,7 +9141,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="44.25" customHeight="1">
-      <c r="A57" s="159"/>
+      <c r="A57" s="150"/>
       <c r="B57" s="54" t="s">
         <v>89</v>
       </c>
@@ -9146,7 +9155,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="32">
-      <c r="A58" s="159"/>
+      <c r="A58" s="150"/>
       <c r="B58" s="54" t="s">
         <v>56</v>
       </c>
@@ -9160,7 +9169,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="30">
-      <c r="A59" s="159"/>
+      <c r="A59" s="150"/>
       <c r="B59" s="54" t="s">
         <v>80</v>
       </c>
@@ -9180,7 +9189,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" s="35" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A60" s="160"/>
+      <c r="A60" s="151"/>
       <c r="B60" s="54" t="s">
         <v>91</v>
       </c>
@@ -9202,21 +9211,21 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="27" customHeight="1">
-      <c r="A61" s="153" t="s">
+      <c r="A61" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="154"/>
-      <c r="C61" s="136"/>
-      <c r="D61" s="131" t="s">
+      <c r="B61" s="144"/>
+      <c r="C61" s="128"/>
+      <c r="D61" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E61" s="131" t="s">
+      <c r="E61" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F61" s="131" t="s">
+      <c r="F61" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="G61" s="133" t="s">
+      <c r="G61" s="138" t="s">
         <v>24</v>
       </c>
       <c r="H61" s="43" t="s">
@@ -9224,79 +9233,79 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="27" customHeight="1">
-      <c r="A62" s="155"/>
-      <c r="B62" s="143"/>
-      <c r="C62" s="136"/>
-      <c r="D62" s="131"/>
-      <c r="E62" s="131"/>
-      <c r="F62" s="131"/>
-      <c r="G62" s="133"/>
+      <c r="A62" s="145"/>
+      <c r="B62" s="146"/>
+      <c r="C62" s="128"/>
+      <c r="D62" s="123"/>
+      <c r="E62" s="123"/>
+      <c r="F62" s="123"/>
+      <c r="G62" s="138"/>
       <c r="H62" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="27" customHeight="1">
-      <c r="A63" s="155"/>
-      <c r="B63" s="143"/>
-      <c r="C63" s="136"/>
-      <c r="D63" s="131"/>
-      <c r="E63" s="131"/>
-      <c r="F63" s="131"/>
-      <c r="G63" s="133"/>
+      <c r="A63" s="145"/>
+      <c r="B63" s="146"/>
+      <c r="C63" s="128"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="123"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="138"/>
       <c r="H63" s="43" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="27" customHeight="1">
-      <c r="A64" s="155"/>
-      <c r="B64" s="143"/>
-      <c r="C64" s="136"/>
-      <c r="D64" s="131"/>
-      <c r="E64" s="131"/>
-      <c r="F64" s="131"/>
-      <c r="G64" s="133"/>
+      <c r="A64" s="145"/>
+      <c r="B64" s="146"/>
+      <c r="C64" s="128"/>
+      <c r="D64" s="123"/>
+      <c r="E64" s="123"/>
+      <c r="F64" s="123"/>
+      <c r="G64" s="138"/>
       <c r="H64" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="27" customHeight="1">
-      <c r="A65" s="155"/>
-      <c r="B65" s="143"/>
-      <c r="C65" s="136"/>
-      <c r="D65" s="131"/>
-      <c r="E65" s="131"/>
-      <c r="F65" s="131"/>
-      <c r="G65" s="133"/>
+      <c r="A65" s="145"/>
+      <c r="B65" s="146"/>
+      <c r="C65" s="128"/>
+      <c r="D65" s="123"/>
+      <c r="E65" s="123"/>
+      <c r="F65" s="123"/>
+      <c r="G65" s="138"/>
       <c r="H65" s="43" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="27" customHeight="1">
-      <c r="A66" s="155"/>
-      <c r="B66" s="143"/>
-      <c r="C66" s="136"/>
-      <c r="D66" s="131"/>
-      <c r="E66" s="131"/>
-      <c r="F66" s="131"/>
-      <c r="G66" s="133"/>
+      <c r="A66" s="145"/>
+      <c r="B66" s="146"/>
+      <c r="C66" s="128"/>
+      <c r="D66" s="123"/>
+      <c r="E66" s="123"/>
+      <c r="F66" s="123"/>
+      <c r="G66" s="138"/>
       <c r="H66" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="27" customHeight="1">
-      <c r="A67" s="156"/>
-      <c r="B67" s="157"/>
-      <c r="C67" s="136"/>
-      <c r="D67" s="131"/>
-      <c r="E67" s="131"/>
-      <c r="F67" s="131"/>
-      <c r="G67" s="133"/>
+      <c r="A67" s="147"/>
+      <c r="B67" s="148"/>
+      <c r="C67" s="128"/>
+      <c r="D67" s="123"/>
+      <c r="E67" s="123"/>
+      <c r="F67" s="123"/>
+      <c r="G67" s="138"/>
       <c r="H67" s="43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="64" hidden="1">
-      <c r="A68" s="134" t="s">
+    <row r="68" spans="1:8" ht="409.6" hidden="1">
+      <c r="A68" s="116" t="s">
         <v>64</v>
       </c>
       <c r="B68" s="53"/>
@@ -9319,8 +9328,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="64">
-      <c r="A69" s="134"/>
+    <row r="69" spans="1:8" ht="409.6">
+      <c r="A69" s="116"/>
       <c r="B69" s="53" t="s">
         <v>65</v>
       </c>
@@ -9341,7 +9350,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="64">
+    <row r="70" spans="1:8" ht="350">
       <c r="A70" s="53" t="s">
         <v>45</v>
       </c>
@@ -9375,49 +9384,49 @@
       <c r="C71" s="1"/>
     </row>
     <row r="72" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A72" s="149" t="s">
+      <c r="A72" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="B72" s="150"/>
-      <c r="C72" s="147" t="s">
+      <c r="B72" s="140"/>
+      <c r="C72" s="115" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="62" t="s">
         <v>7</v>
       </c>
       <c r="E72" s="62"/>
-      <c r="F72" s="146" t="s">
+      <c r="F72" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="147" t="s">
+      <c r="G72" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="H72" s="147" t="s">
+      <c r="H72" s="115" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A73" s="151"/>
-      <c r="B73" s="152"/>
-      <c r="C73" s="147"/>
+      <c r="A73" s="141"/>
+      <c r="B73" s="142"/>
+      <c r="C73" s="115"/>
       <c r="D73" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F73" s="146"/>
-      <c r="G73" s="147"/>
-      <c r="H73" s="147"/>
+      <c r="F73" s="154"/>
+      <c r="G73" s="115"/>
+      <c r="H73" s="115"/>
     </row>
     <row r="74" spans="1:8" ht="91.5" customHeight="1">
-      <c r="A74" s="122" t="s">
+      <c r="A74" s="131" t="s">
         <v>61</v>
       </c>
       <c r="B74" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="152" t="s">
         <v>82</v>
       </c>
       <c r="D74" s="22" t="s">
@@ -9429,7 +9438,7 @@
       <c r="F74" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G74" s="127" t="s">
+      <c r="G74" s="113" t="s">
         <v>83</v>
       </c>
       <c r="H74" s="21" t="s">
@@ -9437,11 +9446,11 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="124.5" customHeight="1">
-      <c r="A75" s="123"/>
+      <c r="A75" s="132"/>
       <c r="B75" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="145"/>
+      <c r="C75" s="153"/>
       <c r="D75" s="34" t="s">
         <v>5</v>
       </c>
@@ -9451,13 +9460,13 @@
       <c r="F75" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G75" s="129"/>
+      <c r="G75" s="114"/>
       <c r="H75" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="77.25" customHeight="1">
-      <c r="A76" s="124"/>
+      <c r="A76" s="133"/>
       <c r="B76" s="32" t="s">
         <v>98</v>
       </c>
@@ -9738,6 +9747,75 @@
     </row>
   </sheetData>
   <mergeCells count="85">
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="A9:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="G43:G54"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="E61:E67"/>
+    <mergeCell ref="F61:F67"/>
+    <mergeCell ref="G61:G67"/>
+    <mergeCell ref="F37:F54"/>
+    <mergeCell ref="A72:B73"/>
+    <mergeCell ref="A61:B67"/>
+    <mergeCell ref="C61:C67"/>
+    <mergeCell ref="D61:D67"/>
+    <mergeCell ref="A36:A60"/>
+    <mergeCell ref="D37:D54"/>
+    <mergeCell ref="E37:E54"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="G30:G35"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="C33:C34"/>
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="A7:B8"/>
@@ -9754,75 +9832,6 @@
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="G30:G35"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="G43:G54"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="E61:E67"/>
-    <mergeCell ref="F61:F67"/>
-    <mergeCell ref="G61:G67"/>
-    <mergeCell ref="F37:F54"/>
-    <mergeCell ref="A72:B73"/>
-    <mergeCell ref="A61:B67"/>
-    <mergeCell ref="C61:C67"/>
-    <mergeCell ref="D61:D67"/>
-    <mergeCell ref="A36:A60"/>
-    <mergeCell ref="D37:D54"/>
-    <mergeCell ref="E37:E54"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="A9:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="B24:B26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9890,57 +9899,57 @@
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147" t="s">
+      <c r="B5" s="115"/>
+      <c r="C5" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="167" t="s">
+      <c r="E5" s="118" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="168"/>
-      <c r="G5" s="147" t="s">
+      <c r="F5" s="119"/>
+      <c r="G5" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="147" t="s">
+      <c r="H5" s="115" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A6" s="147"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="147"/>
-      <c r="D6" s="169"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="115"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="120"/>
       <c r="E6" s="90" t="s">
         <v>211</v>
       </c>
       <c r="F6" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="147"/>
-      <c r="H6" s="147"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
     </row>
     <row r="7" spans="1:8" ht="176">
-      <c r="A7" s="149" t="s">
+      <c r="A7" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="150"/>
-      <c r="C7" s="140" t="s">
+      <c r="B7" s="140"/>
+      <c r="C7" s="135" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="122" t="s">
+      <c r="D7" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="122" t="s">
+      <c r="E7" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="191"/>
-      <c r="G7" s="200" t="s">
+      <c r="F7" s="190"/>
+      <c r="G7" s="197" t="s">
         <v>214</v>
       </c>
       <c r="H7" s="65" t="s">
@@ -9948,58 +9957,58 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="80">
-      <c r="A8" s="198"/>
-      <c r="B8" s="199"/>
-      <c r="C8" s="141"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="195"/>
-      <c r="G8" s="201"/>
+      <c r="A8" s="195"/>
+      <c r="B8" s="196"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="198"/>
       <c r="H8" s="51" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="48">
-      <c r="A9" s="198"/>
-      <c r="B9" s="199"/>
-      <c r="C9" s="141"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="195"/>
-      <c r="G9" s="201"/>
+      <c r="A9" s="195"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="198"/>
       <c r="H9" s="13" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="128">
-      <c r="A10" s="198"/>
-      <c r="B10" s="199"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="195"/>
-      <c r="G10" s="201"/>
+      <c r="A10" s="195"/>
+      <c r="B10" s="196"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="191"/>
+      <c r="G10" s="198"/>
       <c r="H10" s="19" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="48">
-      <c r="A11" s="151"/>
-      <c r="B11" s="152"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
+      <c r="A11" s="141"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
       <c r="F11" s="192"/>
-      <c r="G11" s="202"/>
+      <c r="G11" s="199"/>
       <c r="H11" s="30" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="173.25" customHeight="1">
-      <c r="A12" s="196" t="s">
+      <c r="A12" s="193" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="197"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="63" t="s">
         <v>33</v>
       </c>
@@ -10014,10 +10023,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="173.25" customHeight="1">
-      <c r="A13" s="196" t="s">
+      <c r="A13" s="193" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="197"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="63" t="s">
         <v>35</v>
       </c>
@@ -10032,10 +10041,10 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="256">
-      <c r="A14" s="196" t="s">
+      <c r="A14" s="193" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="197"/>
+      <c r="B14" s="194"/>
       <c r="C14" s="63" t="s">
         <v>218</v>
       </c>
@@ -10050,10 +10059,10 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="322.5" customHeight="1">
-      <c r="A15" s="196" t="s">
+      <c r="A15" s="193" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="197"/>
+      <c r="B15" s="194"/>
       <c r="C15" s="110" t="s">
         <v>237</v>
       </c>
@@ -10068,16 +10077,16 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="76.5" customHeight="1">
-      <c r="A16" s="149" t="s">
+      <c r="A16" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="150"/>
-      <c r="C16" s="140" t="s">
+      <c r="B16" s="140"/>
+      <c r="C16" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="191"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="190"/>
       <c r="G16" s="65" t="s">
         <v>39</v>
       </c>
@@ -10086,11 +10095,11 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="58.5" customHeight="1">
-      <c r="A17" s="151"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
+      <c r="A17" s="141"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
       <c r="F17" s="192"/>
       <c r="G17" s="65" t="s">
         <v>40</v>
@@ -10100,17 +10109,17 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="35.25" customHeight="1">
-      <c r="A18" s="149" t="s">
+      <c r="A18" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="150"/>
-      <c r="C18" s="140" t="s">
+      <c r="B18" s="140"/>
+      <c r="C18" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="191"/>
-      <c r="G18" s="193" t="s">
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="190"/>
+      <c r="G18" s="203" t="s">
         <v>220</v>
       </c>
       <c r="H18" s="46" t="s">
@@ -10118,22 +10127,22 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A19" s="151"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="148"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="124"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="142"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
       <c r="F19" s="192"/>
-      <c r="G19" s="194"/>
+      <c r="G19" s="204"/>
       <c r="H19" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="168" customHeight="1">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="134"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="27" t="s">
         <v>185</v>
       </c>
@@ -10152,19 +10161,19 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="153.75" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="134"/>
-      <c r="C21" s="136" t="s">
+      <c r="A21" s="116"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="128" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="131" t="s">
+      <c r="E21" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="132"/>
-      <c r="G21" s="133" t="s">
+      <c r="F21" s="157"/>
+      <c r="G21" s="138" t="s">
         <v>189</v>
       </c>
       <c r="H21" s="28" t="s">
@@ -10172,66 +10181,66 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="133"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="138"/>
       <c r="H22" s="92" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A23" s="134" t="s">
+      <c r="A23" s="116" t="s">
         <v>191</v>
       </c>
-      <c r="B23" s="134"/>
-      <c r="C23" s="130" t="s">
+      <c r="B23" s="116"/>
+      <c r="C23" s="122" t="s">
         <v>192</v>
       </c>
-      <c r="D23" s="131" t="s">
+      <c r="D23" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="131" t="s">
+      <c r="E23" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="132"/>
-      <c r="G23" s="137" t="s">
+      <c r="F23" s="157"/>
+      <c r="G23" s="117" t="s">
         <v>193</v>
       </c>
-      <c r="H23" s="137" t="s">
+      <c r="H23" s="117" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="137"/>
-      <c r="H24" s="137"/>
+      <c r="A24" s="116"/>
+      <c r="B24" s="116"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
     </row>
     <row r="25" spans="1:8" ht="108" customHeight="1">
-      <c r="A25" s="171" t="s">
+      <c r="A25" s="124" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="171"/>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="171"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="124"/>
     </row>
     <row r="26" spans="1:8" ht="58.5" customHeight="1">
-      <c r="A26" s="134" t="s">
+      <c r="A26" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="134"/>
+      <c r="B26" s="116"/>
       <c r="C26" s="88" t="s">
         <v>197</v>
       </c>
@@ -10248,53 +10257,53 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="96" customHeight="1">
-      <c r="A27" s="170" t="s">
+      <c r="A27" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="170"/>
-      <c r="C27" s="136" t="s">
+      <c r="B27" s="121"/>
+      <c r="C27" s="128" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="131" t="s">
+      <c r="D27" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="131" t="s">
+      <c r="E27" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="132"/>
-      <c r="G27" s="135"/>
+      <c r="F27" s="157"/>
+      <c r="G27" s="161"/>
       <c r="H27" s="15" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A28" s="170"/>
-      <c r="B28" s="170"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="135"/>
+      <c r="A28" s="121"/>
+      <c r="B28" s="121"/>
+      <c r="C28" s="128"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="157"/>
+      <c r="G28" s="161"/>
       <c r="H28" s="93" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="60" customHeight="1">
-      <c r="A29" s="170"/>
-      <c r="B29" s="170"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="135"/>
+      <c r="A29" s="121"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="123"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="157"/>
+      <c r="G29" s="161"/>
       <c r="H29" s="15" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="105.75" customHeight="1">
-      <c r="A30" s="170"/>
-      <c r="B30" s="170"/>
-      <c r="C30" s="130" t="s">
+      <c r="A30" s="121"/>
+      <c r="B30" s="121"/>
+      <c r="C30" s="122" t="s">
         <v>203</v>
       </c>
       <c r="D30" s="26" t="s">
@@ -10304,7 +10313,7 @@
         <v>5</v>
       </c>
       <c r="F30" s="64"/>
-      <c r="G30" s="126" t="s">
+      <c r="G30" s="165" t="s">
         <v>204</v>
       </c>
       <c r="H30" s="16" t="s">
@@ -10312,9 +10321,9 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="93.75" customHeight="1">
-      <c r="A31" s="170"/>
-      <c r="B31" s="170"/>
-      <c r="C31" s="130"/>
+      <c r="A31" s="121"/>
+      <c r="B31" s="121"/>
+      <c r="C31" s="122"/>
       <c r="D31" s="26" t="s">
         <v>5</v>
       </c>
@@ -10322,46 +10331,46 @@
         <v>5</v>
       </c>
       <c r="F31" s="64"/>
-      <c r="G31" s="126"/>
+      <c r="G31" s="165"/>
       <c r="H31" s="15" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A32" s="142" t="s">
+      <c r="A32" s="160" t="s">
         <v>207</v>
       </c>
-      <c r="B32" s="143"/>
-      <c r="C32" s="112" t="s">
+      <c r="B32" s="146"/>
+      <c r="C32" s="158" t="s">
         <v>208</v>
       </c>
-      <c r="D32" s="122" t="s">
+      <c r="D32" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="122" t="s">
+      <c r="E32" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="120"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127" t="s">
+      <c r="F32" s="162"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="113" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A33" s="142"/>
-      <c r="B33" s="143"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="121"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="129"/>
+      <c r="A33" s="160"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="133"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="163"/>
+      <c r="G33" s="114"/>
+      <c r="H33" s="114"/>
     </row>
     <row r="34" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A34" s="118" t="s">
+      <c r="A34" s="171" t="s">
         <v>233</v>
       </c>
-      <c r="B34" s="119"/>
+      <c r="B34" s="172"/>
       <c r="C34" s="100"/>
       <c r="D34" s="101"/>
       <c r="E34" s="101"/>
@@ -10372,17 +10381,17 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="48">
-      <c r="A35" s="117" t="s">
+      <c r="A35" s="170" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="117" t="s">
+      <c r="B35" s="170" t="s">
         <v>222</v>
       </c>
-      <c r="C35" s="112"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="127" t="s">
+      <c r="C35" s="158"/>
+      <c r="D35" s="131"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="113" t="s">
         <v>225</v>
       </c>
       <c r="H35" s="99" t="s">
@@ -10390,32 +10399,32 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A36" s="115"/>
-      <c r="B36" s="115"/>
-      <c r="C36" s="113"/>
-      <c r="D36" s="123"/>
-      <c r="E36" s="123"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="128"/>
+      <c r="A36" s="168"/>
+      <c r="B36" s="168"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="164"/>
+      <c r="G36" s="166"/>
       <c r="H36" s="25" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="32">
-      <c r="A37" s="115"/>
-      <c r="B37" s="116"/>
-      <c r="C37" s="114"/>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="129"/>
+      <c r="A37" s="168"/>
+      <c r="B37" s="169"/>
+      <c r="C37" s="159"/>
+      <c r="D37" s="133"/>
+      <c r="E37" s="133"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="114"/>
       <c r="H37" s="25" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="192">
-      <c r="A38" s="115"/>
-      <c r="B38" s="115" t="s">
+      <c r="A38" s="168"/>
+      <c r="B38" s="168" t="s">
         <v>223</v>
       </c>
       <c r="C38" s="97"/>
@@ -10430,8 +10439,8 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A39" s="116"/>
-      <c r="B39" s="116"/>
+      <c r="A39" s="169"/>
+      <c r="B39" s="169"/>
       <c r="C39" s="97"/>
       <c r="D39" s="34"/>
       <c r="E39" s="34"/>
@@ -10442,10 +10451,10 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="58.5" customHeight="1">
-      <c r="A40" s="189" t="s">
+      <c r="A40" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="190"/>
+      <c r="B40" s="201"/>
       <c r="C40" s="33"/>
       <c r="D40" s="26" t="s">
         <v>0</v>
@@ -10464,43 +10473,43 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="124.5" customHeight="1">
-      <c r="A41" s="163" t="s">
+      <c r="A41" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="163" t="s">
+      <c r="B41" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="136" t="s">
+      <c r="C41" s="128" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="122" t="s">
+      <c r="E41" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="F41" s="122" t="s">
+      <c r="F41" s="131" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="164" t="s">
+      <c r="G41" s="129" t="s">
         <v>142</v>
       </c>
-      <c r="H41" s="165" t="s">
+      <c r="H41" s="202" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="141" customHeight="1">
-      <c r="A42" s="163"/>
-      <c r="B42" s="163"/>
-      <c r="C42" s="136"/>
+      <c r="A42" s="127"/>
+      <c r="B42" s="127"/>
+      <c r="C42" s="128"/>
       <c r="D42" s="26"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="123"/>
-      <c r="G42" s="164"/>
-      <c r="H42" s="165"/>
+      <c r="E42" s="132"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="129"/>
+      <c r="H42" s="202"/>
     </row>
     <row r="43" spans="1:8" ht="285.75" customHeight="1">
-      <c r="A43" s="163"/>
+      <c r="A43" s="127"/>
       <c r="B43" s="40" t="s">
         <v>11</v>
       </c>
@@ -10508,33 +10517,33 @@
       <c r="D43" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E43" s="124"/>
-      <c r="F43" s="124"/>
-      <c r="G43" s="164"/>
+      <c r="E43" s="133"/>
+      <c r="F43" s="133"/>
+      <c r="G43" s="129"/>
       <c r="H43" s="36" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="36.75" customHeight="1">
-      <c r="A44" s="163"/>
+      <c r="A44" s="127"/>
       <c r="B44" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="166"/>
+      <c r="C44" s="134"/>
       <c r="D44" s="26"/>
       <c r="E44"/>
       <c r="F44" s="26"/>
-      <c r="G44" s="164"/>
-      <c r="H44" s="161" t="s">
+      <c r="G44" s="129"/>
+      <c r="H44" s="125" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="78" customHeight="1">
-      <c r="A45" s="163"/>
+      <c r="A45" s="127"/>
       <c r="B45" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="C45" s="166"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="26" t="s">
         <v>0</v>
       </c>
@@ -10544,11 +10553,11 @@
       <c r="F45" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G45" s="164"/>
-      <c r="H45" s="162"/>
+      <c r="G45" s="129"/>
+      <c r="H45" s="126"/>
     </row>
     <row r="46" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A46" s="163"/>
+      <c r="A46" s="127"/>
       <c r="B46" s="54" t="s">
         <v>12</v>
       </c>
@@ -10562,13 +10571,13 @@
       <c r="F46" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G46" s="164"/>
+      <c r="G46" s="129"/>
       <c r="H46" s="47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="136.5" customHeight="1">
-      <c r="A47" s="158" t="s">
+      <c r="A47" s="149" t="s">
         <v>92</v>
       </c>
       <c r="B47" s="54" t="s">
@@ -10592,18 +10601,18 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="285.75" customHeight="1">
-      <c r="A48" s="159"/>
-      <c r="B48" s="138" t="s">
+      <c r="A48" s="150"/>
+      <c r="B48" s="155" t="s">
         <v>71</v>
       </c>
       <c r="C48" s="38"/>
-      <c r="D48" s="122" t="s">
+      <c r="D48" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="131" t="s">
+      <c r="E48" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="F48" s="131" t="s">
+      <c r="F48" s="123" t="s">
         <v>70</v>
       </c>
       <c r="G48" s="41" t="s">
@@ -10614,237 +10623,237 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="335">
-      <c r="A49" s="159"/>
-      <c r="B49" s="139"/>
+      <c r="A49" s="150"/>
+      <c r="B49" s="156"/>
       <c r="C49" s="38"/>
-      <c r="D49" s="123"/>
-      <c r="E49" s="131"/>
-      <c r="F49" s="131"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="123"/>
+      <c r="F49" s="123"/>
       <c r="G49" s="41"/>
       <c r="H49" s="107" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="258" customHeight="1">
-      <c r="A50" s="159"/>
+      <c r="A50" s="150"/>
       <c r="B50" s="98"/>
       <c r="C50" s="38"/>
-      <c r="D50" s="123"/>
-      <c r="E50" s="131"/>
-      <c r="F50" s="131"/>
+      <c r="D50" s="132"/>
+      <c r="E50" s="123"/>
+      <c r="F50" s="123"/>
       <c r="G50" s="41"/>
       <c r="H50" s="107" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="254.25" customHeight="1">
-      <c r="A51" s="159"/>
+      <c r="A51" s="150"/>
       <c r="B51" s="98"/>
       <c r="C51" s="38"/>
-      <c r="D51" s="123"/>
-      <c r="E51" s="131"/>
-      <c r="F51" s="131"/>
+      <c r="D51" s="132"/>
+      <c r="E51" s="123"/>
+      <c r="F51" s="123"/>
       <c r="G51" s="41"/>
       <c r="H51" s="107" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="206.25" customHeight="1">
-      <c r="A52" s="159"/>
-      <c r="B52" s="139" t="s">
+      <c r="A52" s="150"/>
+      <c r="B52" s="156" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="140"/>
-      <c r="D52" s="123"/>
-      <c r="E52" s="131"/>
-      <c r="F52" s="131"/>
-      <c r="G52" s="140"/>
+      <c r="C52" s="135"/>
+      <c r="D52" s="132"/>
+      <c r="E52" s="123"/>
+      <c r="F52" s="123"/>
+      <c r="G52" s="135"/>
       <c r="H52" s="108" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="192">
-      <c r="A53" s="159"/>
-      <c r="B53" s="139"/>
-      <c r="C53" s="141"/>
-      <c r="D53" s="123"/>
-      <c r="E53" s="131"/>
-      <c r="F53" s="131"/>
-      <c r="G53" s="148"/>
+      <c r="A53" s="150"/>
+      <c r="B53" s="156"/>
+      <c r="C53" s="136"/>
+      <c r="D53" s="132"/>
+      <c r="E53" s="123"/>
+      <c r="F53" s="123"/>
+      <c r="G53" s="137"/>
       <c r="H53" s="108" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="16">
-      <c r="A54" s="159"/>
+      <c r="A54" s="150"/>
       <c r="B54" s="54" t="s">
         <v>72</v>
       </c>
       <c r="C54" s="17"/>
-      <c r="D54" s="123"/>
-      <c r="E54" s="131"/>
-      <c r="F54" s="131"/>
-      <c r="G54" s="140"/>
+      <c r="D54" s="132"/>
+      <c r="E54" s="123"/>
+      <c r="F54" s="123"/>
+      <c r="G54" s="135"/>
       <c r="H54" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="16">
-      <c r="A55" s="159"/>
+      <c r="A55" s="150"/>
       <c r="B55" s="54" t="s">
         <v>73</v>
       </c>
       <c r="C55" s="17"/>
-      <c r="D55" s="123"/>
-      <c r="E55" s="131"/>
-      <c r="F55" s="131"/>
-      <c r="G55" s="141"/>
+      <c r="D55" s="132"/>
+      <c r="E55" s="123"/>
+      <c r="F55" s="123"/>
+      <c r="G55" s="136"/>
       <c r="H55" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="16">
-      <c r="A56" s="159"/>
+      <c r="A56" s="150"/>
       <c r="B56" s="54" t="s">
         <v>74</v>
       </c>
       <c r="C56" s="17"/>
-      <c r="D56" s="123"/>
-      <c r="E56" s="131"/>
-      <c r="F56" s="131"/>
-      <c r="G56" s="141"/>
+      <c r="D56" s="132"/>
+      <c r="E56" s="123"/>
+      <c r="F56" s="123"/>
+      <c r="G56" s="136"/>
       <c r="H56" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="16">
-      <c r="A57" s="159"/>
+      <c r="A57" s="150"/>
       <c r="B57" s="54" t="s">
         <v>75</v>
       </c>
       <c r="C57" s="17"/>
-      <c r="D57" s="123"/>
-      <c r="E57" s="131"/>
-      <c r="F57" s="131"/>
-      <c r="G57" s="141"/>
+      <c r="D57" s="132"/>
+      <c r="E57" s="123"/>
+      <c r="F57" s="123"/>
+      <c r="G57" s="136"/>
       <c r="H57" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="16">
-      <c r="A58" s="159"/>
+      <c r="A58" s="150"/>
       <c r="B58" s="54" t="s">
         <v>76</v>
       </c>
       <c r="C58" s="17"/>
-      <c r="D58" s="123"/>
-      <c r="E58" s="131"/>
-      <c r="F58" s="131"/>
-      <c r="G58" s="141"/>
+      <c r="D58" s="132"/>
+      <c r="E58" s="123"/>
+      <c r="F58" s="123"/>
+      <c r="G58" s="136"/>
       <c r="H58" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="16">
-      <c r="A59" s="159"/>
+      <c r="A59" s="150"/>
       <c r="B59" s="54" t="s">
         <v>77</v>
       </c>
       <c r="C59" s="17"/>
-      <c r="D59" s="123"/>
-      <c r="E59" s="131"/>
-      <c r="F59" s="131"/>
-      <c r="G59" s="141"/>
+      <c r="D59" s="132"/>
+      <c r="E59" s="123"/>
+      <c r="F59" s="123"/>
+      <c r="G59" s="136"/>
       <c r="H59" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="16">
-      <c r="A60" s="159"/>
+      <c r="A60" s="150"/>
       <c r="B60" s="54" t="s">
         <v>78</v>
       </c>
       <c r="C60" s="17"/>
-      <c r="D60" s="123"/>
-      <c r="E60" s="131"/>
-      <c r="F60" s="131"/>
-      <c r="G60" s="141"/>
+      <c r="D60" s="132"/>
+      <c r="E60" s="123"/>
+      <c r="F60" s="123"/>
+      <c r="G60" s="136"/>
       <c r="H60" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="16">
-      <c r="A61" s="159"/>
+      <c r="A61" s="150"/>
       <c r="B61" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C61" s="17"/>
-      <c r="D61" s="123"/>
-      <c r="E61" s="131"/>
-      <c r="F61" s="131"/>
-      <c r="G61" s="141"/>
+      <c r="D61" s="132"/>
+      <c r="E61" s="123"/>
+      <c r="F61" s="123"/>
+      <c r="G61" s="136"/>
       <c r="H61" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="16">
-      <c r="A62" s="159"/>
+      <c r="A62" s="150"/>
       <c r="B62" s="54" t="s">
         <v>90</v>
       </c>
       <c r="C62" s="17"/>
-      <c r="D62" s="123"/>
-      <c r="E62" s="131"/>
-      <c r="F62" s="131"/>
-      <c r="G62" s="141"/>
+      <c r="D62" s="132"/>
+      <c r="E62" s="123"/>
+      <c r="F62" s="123"/>
+      <c r="G62" s="136"/>
       <c r="H62" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="18" customHeight="1">
-      <c r="A63" s="159"/>
+      <c r="A63" s="150"/>
       <c r="B63" s="54" t="s">
         <v>88</v>
       </c>
       <c r="C63" s="17"/>
-      <c r="D63" s="123"/>
-      <c r="E63" s="131"/>
-      <c r="F63" s="131"/>
-      <c r="G63" s="141"/>
+      <c r="D63" s="132"/>
+      <c r="E63" s="123"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="136"/>
       <c r="H63" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="32">
-      <c r="A64" s="159"/>
+      <c r="A64" s="150"/>
       <c r="B64" s="54" t="s">
         <v>126</v>
       </c>
       <c r="C64" s="17"/>
-      <c r="D64" s="123"/>
-      <c r="E64" s="131"/>
-      <c r="F64" s="131"/>
-      <c r="G64" s="141"/>
+      <c r="D64" s="132"/>
+      <c r="E64" s="123"/>
+      <c r="F64" s="123"/>
+      <c r="G64" s="136"/>
       <c r="H64" s="49" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="39.75" customHeight="1">
-      <c r="A65" s="159"/>
+      <c r="A65" s="150"/>
       <c r="B65" s="54" t="s">
         <v>127</v>
       </c>
       <c r="C65" s="17"/>
-      <c r="D65" s="123"/>
-      <c r="E65" s="131"/>
-      <c r="F65" s="131"/>
-      <c r="G65" s="148"/>
+      <c r="D65" s="132"/>
+      <c r="E65" s="123"/>
+      <c r="F65" s="123"/>
+      <c r="G65" s="137"/>
       <c r="H65" s="49" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="30">
-      <c r="A66" s="159"/>
+      <c r="A66" s="150"/>
       <c r="B66" s="45" t="s">
         <v>105</v>
       </c>
@@ -10866,7 +10875,7 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="44.25" customHeight="1">
-      <c r="A67" s="159"/>
+      <c r="A67" s="150"/>
       <c r="B67" s="54" t="s">
         <v>79</v>
       </c>
@@ -10880,7 +10889,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="44.25" customHeight="1">
-      <c r="A68" s="159"/>
+      <c r="A68" s="150"/>
       <c r="B68" s="54" t="s">
         <v>89</v>
       </c>
@@ -10894,7 +10903,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="32">
-      <c r="A69" s="159"/>
+      <c r="A69" s="150"/>
       <c r="B69" s="54" t="s">
         <v>56</v>
       </c>
@@ -10908,7 +10917,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="30">
-      <c r="A70" s="159"/>
+      <c r="A70" s="150"/>
       <c r="B70" s="54" t="s">
         <v>80</v>
       </c>
@@ -10928,7 +10937,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" s="35" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A71" s="160"/>
+      <c r="A71" s="151"/>
       <c r="B71" s="54" t="s">
         <v>91</v>
       </c>
@@ -10950,21 +10959,21 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="27" customHeight="1">
-      <c r="A72" s="153" t="s">
+      <c r="A72" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="154"/>
-      <c r="C72" s="136"/>
-      <c r="D72" s="131" t="s">
+      <c r="B72" s="144"/>
+      <c r="C72" s="128"/>
+      <c r="D72" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="E72" s="131" t="s">
+      <c r="E72" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="131" t="s">
+      <c r="F72" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="G72" s="133" t="s">
+      <c r="G72" s="138" t="s">
         <v>24</v>
       </c>
       <c r="H72" s="43" t="s">
@@ -10972,82 +10981,82 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="27" customHeight="1">
-      <c r="A73" s="155"/>
-      <c r="B73" s="143"/>
-      <c r="C73" s="136"/>
-      <c r="D73" s="131"/>
-      <c r="E73" s="131"/>
-      <c r="F73" s="131"/>
-      <c r="G73" s="133"/>
+      <c r="A73" s="145"/>
+      <c r="B73" s="146"/>
+      <c r="C73" s="128"/>
+      <c r="D73" s="123"/>
+      <c r="E73" s="123"/>
+      <c r="F73" s="123"/>
+      <c r="G73" s="138"/>
       <c r="H73" s="18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="27" customHeight="1">
-      <c r="A74" s="155"/>
-      <c r="B74" s="143"/>
-      <c r="C74" s="136"/>
-      <c r="D74" s="131"/>
-      <c r="E74" s="131"/>
-      <c r="F74" s="131"/>
-      <c r="G74" s="133"/>
+      <c r="A74" s="145"/>
+      <c r="B74" s="146"/>
+      <c r="C74" s="128"/>
+      <c r="D74" s="123"/>
+      <c r="E74" s="123"/>
+      <c r="F74" s="123"/>
+      <c r="G74" s="138"/>
       <c r="H74" s="43" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="27" customHeight="1">
-      <c r="A75" s="155"/>
-      <c r="B75" s="143"/>
-      <c r="C75" s="136"/>
-      <c r="D75" s="131"/>
-      <c r="E75" s="131"/>
-      <c r="F75" s="131"/>
-      <c r="G75" s="133"/>
+      <c r="A75" s="145"/>
+      <c r="B75" s="146"/>
+      <c r="C75" s="128"/>
+      <c r="D75" s="123"/>
+      <c r="E75" s="123"/>
+      <c r="F75" s="123"/>
+      <c r="G75" s="138"/>
       <c r="H75" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="27" customHeight="1">
-      <c r="A76" s="155"/>
-      <c r="B76" s="143"/>
-      <c r="C76" s="136"/>
-      <c r="D76" s="131"/>
-      <c r="E76" s="131"/>
-      <c r="F76" s="131"/>
-      <c r="G76" s="133"/>
+      <c r="A76" s="145"/>
+      <c r="B76" s="146"/>
+      <c r="C76" s="128"/>
+      <c r="D76" s="123"/>
+      <c r="E76" s="123"/>
+      <c r="F76" s="123"/>
+      <c r="G76" s="138"/>
       <c r="H76" s="43" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="27" customHeight="1">
-      <c r="A77" s="155"/>
-      <c r="B77" s="143"/>
-      <c r="C77" s="136"/>
-      <c r="D77" s="131"/>
-      <c r="E77" s="131"/>
-      <c r="F77" s="131"/>
-      <c r="G77" s="133"/>
+      <c r="A77" s="145"/>
+      <c r="B77" s="146"/>
+      <c r="C77" s="128"/>
+      <c r="D77" s="123"/>
+      <c r="E77" s="123"/>
+      <c r="F77" s="123"/>
+      <c r="G77" s="138"/>
       <c r="H77" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="27" customHeight="1">
-      <c r="A78" s="156"/>
-      <c r="B78" s="157"/>
-      <c r="C78" s="136"/>
-      <c r="D78" s="131"/>
-      <c r="E78" s="131"/>
-      <c r="F78" s="131"/>
-      <c r="G78" s="133"/>
+      <c r="A78" s="147"/>
+      <c r="B78" s="148"/>
+      <c r="C78" s="128"/>
+      <c r="D78" s="123"/>
+      <c r="E78" s="123"/>
+      <c r="F78" s="123"/>
+      <c r="G78" s="138"/>
       <c r="H78" s="43" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="100.5" customHeight="1">
-      <c r="A79" s="189" t="s">
+      <c r="A79" s="200" t="s">
         <v>240</v>
       </c>
-      <c r="B79" s="190"/>
+      <c r="B79" s="201"/>
       <c r="C79" s="27"/>
       <c r="D79" s="26" t="s">
         <v>5</v>
@@ -11066,7 +11075,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="64" hidden="1">
-      <c r="A80" s="134" t="s">
+      <c r="A80" s="116" t="s">
         <v>64</v>
       </c>
       <c r="B80" s="53"/>
@@ -11090,7 +11099,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="64">
-      <c r="A81" s="134"/>
+      <c r="A81" s="116"/>
       <c r="B81" s="53" t="s">
         <v>65</v>
       </c>
@@ -11145,49 +11154,49 @@
       <c r="C83" s="1"/>
     </row>
     <row r="84" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A84" s="149" t="s">
+      <c r="A84" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="150"/>
-      <c r="C84" s="147" t="s">
+      <c r="B84" s="140"/>
+      <c r="C84" s="115" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="62" t="s">
         <v>7</v>
       </c>
       <c r="E84" s="62"/>
-      <c r="F84" s="146" t="s">
+      <c r="F84" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="147" t="s">
+      <c r="G84" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="H84" s="147" t="s">
+      <c r="H84" s="115" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="26.25" customHeight="1">
-      <c r="A85" s="151"/>
-      <c r="B85" s="152"/>
-      <c r="C85" s="147"/>
+      <c r="A85" s="141"/>
+      <c r="B85" s="142"/>
+      <c r="C85" s="115"/>
       <c r="D85" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F85" s="146"/>
-      <c r="G85" s="147"/>
-      <c r="H85" s="147"/>
+      <c r="F85" s="154"/>
+      <c r="G85" s="115"/>
+      <c r="H85" s="115"/>
     </row>
     <row r="86" spans="1:8" ht="91.5" customHeight="1">
-      <c r="A86" s="122" t="s">
+      <c r="A86" s="131" t="s">
         <v>61</v>
       </c>
       <c r="B86" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="144" t="s">
+      <c r="C86" s="152" t="s">
         <v>82</v>
       </c>
       <c r="D86" s="22" t="s">
@@ -11199,7 +11208,7 @@
       <c r="F86" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G86" s="127" t="s">
+      <c r="G86" s="113" t="s">
         <v>83</v>
       </c>
       <c r="H86" s="21" t="s">
@@ -11207,11 +11216,11 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="124.5" customHeight="1">
-      <c r="A87" s="123"/>
+      <c r="A87" s="132"/>
       <c r="B87" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C87" s="145"/>
+      <c r="C87" s="153"/>
       <c r="D87" s="34" t="s">
         <v>5</v>
       </c>
@@ -11221,13 +11230,13 @@
       <c r="F87" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G87" s="129"/>
+      <c r="G87" s="114"/>
       <c r="H87" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="77.25" customHeight="1">
-      <c r="A88" s="124"/>
+      <c r="A88" s="133"/>
       <c r="B88" s="32" t="s">
         <v>98</v>
       </c>
@@ -11508,59 +11517,30 @@
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="A7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B31"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H32:H33"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G46"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="A32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A20:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
     <mergeCell ref="G86:G87"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="A84:B85"/>
@@ -11585,30 +11565,59 @@
     <mergeCell ref="G52:G53"/>
     <mergeCell ref="A86:A88"/>
     <mergeCell ref="C86:C87"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A20:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G46"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B31"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="D7:D11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11634,10 +11643,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="203"/>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
+      <c r="A1" s="205"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="20"/>
@@ -11675,11 +11684,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="211" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211" t="s">
         <v>123</v>
       </c>
     </row>
@@ -11690,110 +11699,120 @@
       <c r="B2" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="204"/>
+      <c r="C2" s="211"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="205" t="s">
+      <c r="A3" s="212" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="213" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="207" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="205"/>
-      <c r="B4" s="207"/>
-      <c r="C4" s="208"/>
+      <c r="A4" s="212"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="207"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="209" t="s">
+      <c r="A5" s="210" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="209" t="s">
+      <c r="B5" s="210" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="207" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="209"/>
-      <c r="B6" s="209"/>
-      <c r="C6" s="208"/>
+      <c r="A6" s="210"/>
+      <c r="B6" s="210"/>
+      <c r="C6" s="207"/>
     </row>
     <row r="7" spans="1:3" ht="18">
-      <c r="A7" s="209" t="s">
+      <c r="A7" s="210" t="s">
         <v>114</v>
       </c>
       <c r="B7" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="208" t="s">
+      <c r="C7" s="207" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18">
-      <c r="A8" s="209"/>
+      <c r="A8" s="210"/>
       <c r="B8" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="208"/>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="211" t="s">
+      <c r="A9" s="208" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="211" t="s">
+      <c r="B9" s="208" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="207" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="211"/>
-      <c r="B10" s="211"/>
-      <c r="C10" s="208"/>
+      <c r="A10" s="208"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="207"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="212" t="s">
+      <c r="A11" s="209" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="212" t="s">
+      <c r="B11" s="209" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="207" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="212"/>
-      <c r="B12" s="212"/>
-      <c r="C12" s="208"/>
+      <c r="A12" s="209"/>
+      <c r="B12" s="209"/>
+      <c r="C12" s="207"/>
     </row>
     <row r="13" spans="1:3" ht="18">
-      <c r="A13" s="210" t="s">
+      <c r="A13" s="206" t="s">
         <v>120</v>
       </c>
       <c r="B13" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="208" t="s">
+      <c r="C13" s="207" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18">
-      <c r="A14" s="210"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="208"/>
+      <c r="C14" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="A9:A10"/>
@@ -11802,16 +11821,6 @@
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
